--- a/Husqvarna modell.xlsx
+++ b/Husqvarna modell.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/augusthodt/Desktop/Aksjemodellering/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88B25451-DE12-9743-98FA-3401B2E3B550}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{105C22D7-8157-254A-92F9-935CFE73A4AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17000" activeTab="1" xr2:uid="{5AE0DF26-B7DD-1242-A60E-253C73A930AF}"/>
+    <workbookView xWindow="25240" yWindow="500" windowWidth="24720" windowHeight="26500" activeTab="3" xr2:uid="{5AE0DF26-B7DD-1242-A60E-253C73A930AF}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
@@ -21,14 +21,8 @@
     <sheet name="Nedsideberegning" sheetId="5" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">SOTP!$A$44:$A$51</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">SOTP!$B$44:$B$51</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">SOTP!$A$44:$A$51</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">SOTP!$B$44:$B$51</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">SOTP!$A$44:$A$51</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">SOTP!$B$44:$B$51</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">SOTP!$A$44:$A$51</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">SOTP!$B$44:$B$51</definedName>
+    <definedName name="_xlchart.v1.0" hidden="1">SOTP!$A$61:$A$68</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">SOTP!$B$61:$B$68</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -675,7 +669,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -718,8 +712,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
@@ -727,17 +719,6 @@
     <xf numFmtId="10" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -746,9 +727,8 @@
     <xf numFmtId="3" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -771,10 +751,10 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:strDim type="cat">
-        <cx:f>_xlchart.v1.6</cx:f>
+        <cx:f>_xlchart.v1.0</cx:f>
       </cx:strDim>
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.7</cx:f>
+        <cx:f>_xlchart.v1.1</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -2147,58 +2127,80 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{9DB21806-1209-484F-B087-67A603E41D39}">
+  <we:reference id="WA200009404" version="1.0.0.8" store="Omex" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200009404" version="1.0.0.8" store="WA200009404" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;502690ec-3ddc-49b6-90b6-2ce3b3bb0774&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D6FABC2-1253-924E-8CB2-F0C03750A097}">
   <dimension ref="A5:A66"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="26" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="16384" width="10.83203125" style="44"/>
+    <col min="1" max="16384" width="10.83203125" style="42"/>
   </cols>
   <sheetData>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" s="43"/>
+      <c r="A5" s="41"/>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" s="43"/>
+      <c r="A6" s="41"/>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" s="43"/>
+      <c r="A7" s="41"/>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" s="43"/>
+      <c r="A8" s="41"/>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" s="43" t="s">
+      <c r="A20" s="41" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21" s="44" t="s">
+      <c r="A21" s="42" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" s="44" t="s">
+      <c r="A22" s="42" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A23" s="44" t="s">
+      <c r="A23" s="42" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A36" s="43" t="s">
+      <c r="A36" s="41" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A51" s="43" t="s">
+      <c r="A51" s="41" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A66" s="43" t="s">
+      <c r="A66" s="41" t="s">
         <v>131</v>
       </c>
     </row>
@@ -2227,12 +2229,9 @@
     <col min="13" max="13" width="11.1640625" style="2" customWidth="1"/>
     <col min="14" max="14" width="11.33203125" style="2" customWidth="1"/>
     <col min="15" max="15" width="10.33203125" style="2" customWidth="1"/>
-    <col min="16" max="17" width="10.83203125" style="2"/>
-    <col min="18" max="18" width="10.83203125" style="45"/>
-    <col min="19" max="19" width="10.83203125" style="4"/>
-    <col min="20" max="34" width="10.83203125" style="2"/>
-    <col min="35" max="35" width="10.83203125" style="4"/>
-    <col min="36" max="46" width="10.83203125" style="2"/>
+    <col min="16" max="35" width="10.83203125" style="2"/>
+    <col min="36" max="36" width="10.83203125" style="4"/>
+    <col min="37" max="46" width="10.83203125" style="2"/>
     <col min="47" max="47" width="14.1640625" style="2" bestFit="1" customWidth="1"/>
     <col min="48" max="48" width="13.33203125" style="2" bestFit="1" customWidth="1"/>
     <col min="49" max="16384" width="10.83203125" style="2"/>
@@ -2302,10 +2301,10 @@
       <c r="Q3" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="R3" s="46" t="s">
+      <c r="R3" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="S3" s="17" t="s">
+      <c r="S3" s="7" t="s">
         <v>36</v>
       </c>
       <c r="T3" s="7" t="s">
@@ -2350,10 +2349,10 @@
       <c r="AH3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="AI3" s="17" t="s">
+      <c r="AI3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="AJ3" s="7" t="s">
+      <c r="AJ3" s="17" t="s">
         <v>19</v>
       </c>
       <c r="AK3" s="7" t="s">
@@ -2389,7 +2388,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="22">
-        <v>41.85</v>
+        <v>45.71</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>55</v>
@@ -2436,11 +2435,14 @@
       <c r="Q4" s="12">
         <v>15277</v>
       </c>
-      <c r="R4" s="47">
+      <c r="R4" s="12">
         <v>9204</v>
       </c>
-      <c r="S4" s="13">
+      <c r="S4" s="12">
         <v>7429</v>
+      </c>
+      <c r="T4" s="12">
+        <v>13962</v>
       </c>
       <c r="Y4" s="12">
         <v>36170</v>
@@ -2472,10 +2474,10 @@
       <c r="AH4" s="12">
         <v>48352</v>
       </c>
-      <c r="AI4" s="13">
+      <c r="AI4" s="12">
         <v>46614</v>
       </c>
-      <c r="AJ4" s="12">
+      <c r="AJ4" s="13">
         <f>AI4*1</f>
         <v>46614</v>
       </c>
@@ -2488,7 +2490,7 @@
         <v>49932.916799999999</v>
       </c>
       <c r="AM4" s="12">
-        <f t="shared" ref="AK4:AS4" si="0">AL4*1.05</f>
+        <f t="shared" ref="AM4:AS4" si="0">AL4*1.05</f>
         <v>52429.562640000004</v>
       </c>
       <c r="AN4" s="12">
@@ -2568,11 +2570,14 @@
       <c r="Q5" s="14">
         <v>-10101</v>
       </c>
-      <c r="R5" s="48">
+      <c r="R5" s="14">
         <v>-6581</v>
       </c>
-      <c r="S5" s="15">
+      <c r="S5" s="14">
         <v>-5660</v>
+      </c>
+      <c r="T5" s="14">
+        <v>-9417</v>
       </c>
       <c r="Y5" s="14">
         <v>-25996</v>
@@ -2604,48 +2609,48 @@
       <c r="AH5" s="14">
         <v>-34053</v>
       </c>
-      <c r="AI5" s="15">
+      <c r="AI5" s="14">
         <v>-32514</v>
       </c>
-      <c r="AJ5" s="14">
-        <f>AJ4*-0.7</f>
-        <v>-32629.8</v>
+      <c r="AJ5" s="15">
+        <f>AJ4*-0.705</f>
+        <v>-32862.869999999995</v>
       </c>
       <c r="AK5" s="14">
-        <f t="shared" ref="AK5:AS5" si="1">AK4*-0.7</f>
-        <v>-33608.693999999996</v>
+        <f t="shared" ref="AK5:AS5" si="1">AK4*-0.705</f>
+        <v>-33848.756099999999</v>
       </c>
       <c r="AL5" s="14">
         <f t="shared" si="1"/>
-        <v>-34953.04176</v>
+        <v>-35202.706343999998</v>
       </c>
       <c r="AM5" s="14">
         <f t="shared" si="1"/>
-        <v>-36700.693848000003</v>
+        <v>-36962.8416612</v>
       </c>
       <c r="AN5" s="14">
         <f t="shared" si="1"/>
-        <v>-38535.728540399999</v>
+        <v>-38810.983744260004</v>
       </c>
       <c r="AO5" s="14">
         <f t="shared" si="1"/>
-        <v>-40462.514967420007</v>
+        <v>-40751.532931473004</v>
       </c>
       <c r="AP5" s="14">
         <f t="shared" si="1"/>
-        <v>-42485.640715791007</v>
+        <v>-42789.109578046664</v>
       </c>
       <c r="AQ5" s="14">
         <f t="shared" si="1"/>
-        <v>-44609.922751580561</v>
+        <v>-44928.565056948995</v>
       </c>
       <c r="AR5" s="14">
         <f t="shared" si="1"/>
-        <v>-46840.418889159591</v>
+        <v>-47174.993309796446</v>
       </c>
       <c r="AS5" s="14">
         <f t="shared" si="1"/>
-        <v>-49182.439833617573</v>
+        <v>-49533.742975286274</v>
       </c>
     </row>
     <row r="6" spans="1:200" x14ac:dyDescent="0.25">
@@ -2654,7 +2659,7 @@
       </c>
       <c r="B6" s="5">
         <f>B4*B5</f>
-        <v>23925.645000000004</v>
+        <v>26132.407000000003</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>57</v>
@@ -2715,97 +2720,101 @@
         <f>SUM(Q4:Q5)</f>
         <v>5176</v>
       </c>
-      <c r="R6" s="48">
+      <c r="R6" s="14">
         <f t="shared" ref="R6:S6" si="3">SUM(R4:R5)</f>
         <v>2623</v>
       </c>
-      <c r="S6" s="15">
+      <c r="S6" s="14">
         <f t="shared" si="3"/>
         <v>1769</v>
       </c>
+      <c r="T6" s="14">
+        <f t="shared" ref="T6" si="4">SUM(T4:T5)</f>
+        <v>4545</v>
+      </c>
       <c r="Y6" s="14">
-        <f t="shared" ref="Y6:AH6" si="4">SUM(Y4:Y5)</f>
+        <f t="shared" ref="Y6:AH6" si="5">SUM(Y4:Y5)</f>
         <v>10174</v>
       </c>
       <c r="Z6" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>11096</v>
       </c>
       <c r="AA6" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>11472</v>
       </c>
       <c r="AB6" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>10502</v>
       </c>
       <c r="AC6" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>12529</v>
       </c>
       <c r="AD6" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>12576</v>
       </c>
       <c r="AE6" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>15513</v>
       </c>
       <c r="AF6" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>14613</v>
       </c>
       <c r="AG6" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>16125</v>
       </c>
       <c r="AH6" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>14299</v>
       </c>
-      <c r="AI6" s="15">
-        <f t="shared" ref="AI6:AS6" si="5">SUM(AI4:AI5)</f>
+      <c r="AI6" s="14">
+        <f t="shared" ref="AI6:AS6" si="6">SUM(AI4:AI5)</f>
         <v>14100</v>
       </c>
-      <c r="AJ6" s="14">
-        <f t="shared" si="5"/>
-        <v>13984.2</v>
+      <c r="AJ6" s="15">
+        <f t="shared" si="6"/>
+        <v>13751.130000000005</v>
       </c>
       <c r="AK6" s="14">
-        <f t="shared" si="5"/>
-        <v>14403.726000000002</v>
+        <f t="shared" si="6"/>
+        <v>14163.6639</v>
       </c>
       <c r="AL6" s="14">
-        <f t="shared" si="5"/>
-        <v>14979.875039999999</v>
+        <f t="shared" si="6"/>
+        <v>14730.210456000001</v>
       </c>
       <c r="AM6" s="14">
-        <f t="shared" si="5"/>
-        <v>15728.868792000001</v>
+        <f t="shared" si="6"/>
+        <v>15466.720978800004</v>
       </c>
       <c r="AN6" s="14">
-        <f t="shared" si="5"/>
-        <v>16515.312231600008</v>
+        <f t="shared" si="6"/>
+        <v>16240.057027740004</v>
       </c>
       <c r="AO6" s="14">
-        <f t="shared" si="5"/>
-        <v>17341.077843180006</v>
+        <f t="shared" si="6"/>
+        <v>17052.059879127009</v>
       </c>
       <c r="AP6" s="14">
-        <f t="shared" si="5"/>
-        <v>18208.131735339011</v>
+        <f t="shared" si="6"/>
+        <v>17904.662873083354</v>
       </c>
       <c r="AQ6" s="14">
-        <f t="shared" si="5"/>
-        <v>19118.53832210596</v>
+        <f t="shared" si="6"/>
+        <v>18799.896016737526</v>
       </c>
       <c r="AR6" s="14">
-        <f t="shared" si="5"/>
-        <v>20074.465238211262</v>
+        <f t="shared" si="6"/>
+        <v>19739.890817574407</v>
       </c>
       <c r="AS6" s="14">
-        <f t="shared" si="5"/>
-        <v>21078.188500121825</v>
+        <f t="shared" si="6"/>
+        <v>20726.885358453124</v>
       </c>
     </row>
     <row r="7" spans="1:200" x14ac:dyDescent="0.25">
@@ -2813,8 +2822,8 @@
         <v>47</v>
       </c>
       <c r="B7" s="5">
-        <f>S39</f>
-        <v>1707</v>
+        <f>T39</f>
+        <v>1708</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>58</v>
@@ -2861,11 +2870,14 @@
       <c r="Q7" s="14">
         <v>-2317</v>
       </c>
-      <c r="R7" s="48">
+      <c r="R7" s="14">
         <v>-1852</v>
       </c>
-      <c r="S7" s="15">
+      <c r="S7" s="14">
         <v>-1802</v>
+      </c>
+      <c r="T7" s="14">
+        <v>-2024</v>
       </c>
       <c r="Y7" s="14">
         <v>-5833</v>
@@ -2897,10 +2909,10 @@
       <c r="AH7" s="14">
         <v>-8587</v>
       </c>
-      <c r="AI7" s="15">
+      <c r="AI7" s="14">
         <v>-8116</v>
       </c>
-      <c r="AJ7" s="14">
+      <c r="AJ7" s="15">
         <f>AI7*0.97</f>
         <v>-7872.5199999999995</v>
       </c>
@@ -2909,35 +2921,35 @@
         <v>-8108.6956</v>
       </c>
       <c r="AL7" s="14">
-        <f t="shared" ref="AL7:AS7" si="6">AK7*1.04</f>
+        <f t="shared" ref="AL7:AS7" si="7">AK7*1.04</f>
         <v>-8433.0434239999995</v>
       </c>
       <c r="AM7" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-8770.3651609600001</v>
       </c>
       <c r="AN7" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-9121.1797673984001</v>
       </c>
       <c r="AO7" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-9486.0269580943368</v>
       </c>
       <c r="AP7" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-9865.4680364181113</v>
       </c>
       <c r="AQ7" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-10260.086757874837</v>
       </c>
       <c r="AR7" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-10670.49022818983</v>
       </c>
       <c r="AS7" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-11097.309837317423</v>
       </c>
     </row>
@@ -2946,8 +2958,8 @@
         <v>48</v>
       </c>
       <c r="B8" s="5">
-        <f>S44+S54</f>
-        <v>9816</v>
+        <f>T44+T54</f>
+        <v>9106</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>59</v>
@@ -2994,11 +3006,14 @@
       <c r="Q8" s="14">
         <v>-797</v>
       </c>
-      <c r="R8" s="48">
+      <c r="R8" s="14">
         <v>-633</v>
       </c>
-      <c r="S8" s="15">
+      <c r="S8" s="14">
         <v>-772</v>
+      </c>
+      <c r="T8" s="14">
+        <v>-835</v>
       </c>
       <c r="Y8" s="14">
         <v>-1532</v>
@@ -3030,47 +3045,47 @@
       <c r="AH8" s="14">
         <v>-3275</v>
       </c>
-      <c r="AI8" s="15">
+      <c r="AI8" s="14">
         <v>-3074</v>
       </c>
-      <c r="AJ8" s="14">
-        <f t="shared" ref="AJ8:AJ9" si="7">AI8*1</f>
+      <c r="AJ8" s="15">
+        <f t="shared" ref="AJ8:AJ9" si="8">AI8*1</f>
         <v>-3074</v>
       </c>
       <c r="AK8" s="14">
-        <f t="shared" ref="AK8:AK9" si="8">AJ8*1.03</f>
+        <f t="shared" ref="AK8:AK9" si="9">AJ8*1.03</f>
         <v>-3166.2200000000003</v>
       </c>
       <c r="AL8" s="14">
-        <f t="shared" ref="AK8:AS9" si="9">AK8*1.04</f>
+        <f t="shared" ref="AL8:AS9" si="10">AK8*1.04</f>
         <v>-3292.8688000000002</v>
       </c>
       <c r="AM8" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-3424.5835520000005</v>
       </c>
       <c r="AN8" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-3561.5668940800006</v>
       </c>
       <c r="AO8" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-3704.0295698432005</v>
       </c>
       <c r="AP8" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-3852.1907526369287</v>
       </c>
       <c r="AQ8" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-4006.2783827424059</v>
       </c>
       <c r="AR8" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-4166.5295180521025</v>
       </c>
       <c r="AS8" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-4333.1906987741868</v>
       </c>
     </row>
@@ -3080,7 +3095,7 @@
       </c>
       <c r="B9" s="6">
         <f>B6-B7+B8</f>
-        <v>32034.645000000004</v>
+        <v>33530.407000000007</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>60</v>
@@ -3127,11 +3142,14 @@
       <c r="Q9" s="14">
         <v>0</v>
       </c>
-      <c r="R9" s="48">
+      <c r="R9" s="14">
         <v>4</v>
       </c>
-      <c r="S9" s="15">
+      <c r="S9" s="14">
         <v>-31</v>
+      </c>
+      <c r="T9" s="14">
+        <v>24</v>
       </c>
       <c r="Y9" s="14">
         <f>23-5</f>
@@ -3170,47 +3188,47 @@
       <c r="AH9" s="14">
         <v>160</v>
       </c>
-      <c r="AI9" s="15">
+      <c r="AI9" s="14">
         <v>-11</v>
       </c>
-      <c r="AJ9" s="14">
-        <f t="shared" si="7"/>
+      <c r="AJ9" s="15">
+        <f t="shared" si="8"/>
         <v>-11</v>
       </c>
       <c r="AK9" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>-11.33</v>
       </c>
       <c r="AL9" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-11.783200000000001</v>
       </c>
       <c r="AM9" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-12.254528000000001</v>
       </c>
       <c r="AN9" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-12.744709120000001</v>
       </c>
       <c r="AO9" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-13.254497484800002</v>
       </c>
       <c r="AP9" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-13.784677384192003</v>
       </c>
       <c r="AQ9" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-14.336064479559683</v>
       </c>
       <c r="AR9" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-14.90950705874207</v>
       </c>
       <c r="AS9" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-15.505887341091753</v>
       </c>
     </row>
@@ -3219,43 +3237,43 @@
         <v>61</v>
       </c>
       <c r="D10" s="12">
-        <f t="shared" ref="D10:M10" si="10">SUM(D6:D9)</f>
+        <f t="shared" ref="D10:M10" si="11">SUM(D6:D9)</f>
         <v>2159</v>
       </c>
       <c r="E10" s="12">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2064</v>
       </c>
       <c r="F10" s="12">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>556</v>
       </c>
       <c r="G10" s="12">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-1737</v>
       </c>
       <c r="H10" s="12">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2364</v>
       </c>
       <c r="I10" s="12">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2101</v>
       </c>
       <c r="J10" s="12">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>398</v>
       </c>
       <c r="K10" s="12">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>-983</v>
       </c>
       <c r="L10" s="12">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1930</v>
       </c>
       <c r="M10" s="12">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1898</v>
       </c>
       <c r="N10" s="12">
@@ -3274,99 +3292,103 @@
         <f>SUM(Q6:Q9)</f>
         <v>2062</v>
       </c>
-      <c r="R10" s="47">
-        <f t="shared" ref="R10" si="11">SUM(R6:R9)</f>
+      <c r="R10" s="12">
+        <f t="shared" ref="R10" si="12">SUM(R6:R9)</f>
         <v>142</v>
       </c>
-      <c r="S10" s="13">
-        <f t="shared" ref="S10" si="12">SUM(S6:S9)</f>
+      <c r="S10" s="12">
+        <f t="shared" ref="S10:T10" si="13">SUM(S6:S9)</f>
         <v>-836</v>
+      </c>
+      <c r="T10" s="12">
+        <f t="shared" si="13"/>
+        <v>1710</v>
       </c>
       <c r="V10" s="14"/>
       <c r="W10" s="14"/>
       <c r="Y10" s="12">
-        <f t="shared" ref="Y10:AH10" si="13">SUM(Y6:Y9)</f>
+        <f t="shared" ref="Y10:AH10" si="14">SUM(Y6:Y9)</f>
         <v>2827</v>
       </c>
       <c r="Z10" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>3218</v>
       </c>
       <c r="AA10" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>3790</v>
       </c>
       <c r="AB10" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2070</v>
       </c>
       <c r="AC10" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>3690</v>
       </c>
       <c r="AD10" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>3669</v>
       </c>
       <c r="AE10" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>5746</v>
       </c>
       <c r="AF10" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>3043</v>
       </c>
       <c r="AG10" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>3880</v>
       </c>
       <c r="AH10" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2597</v>
       </c>
-      <c r="AI10" s="13">
-        <f t="shared" ref="AI10:AS10" si="14">SUM(AI6:AI9)</f>
+      <c r="AI10" s="12">
+        <f t="shared" ref="AI10:AS10" si="15">SUM(AI6:AI9)</f>
         <v>2899</v>
       </c>
-      <c r="AJ10" s="12">
-        <f t="shared" si="14"/>
-        <v>3026.6800000000012</v>
+      <c r="AJ10" s="13">
+        <f t="shared" si="15"/>
+        <v>2793.6100000000051</v>
       </c>
       <c r="AK10" s="12">
-        <f t="shared" si="14"/>
-        <v>3117.4804000000022</v>
+        <f t="shared" si="15"/>
+        <v>2877.4182999999994</v>
       </c>
       <c r="AL10" s="12">
-        <f t="shared" si="14"/>
-        <v>3242.1796159999994</v>
+        <f t="shared" si="15"/>
+        <v>2992.5150320000012</v>
       </c>
       <c r="AM10" s="12">
-        <f t="shared" si="14"/>
-        <v>3521.6655510400005</v>
+        <f t="shared" si="15"/>
+        <v>3259.5177378400031</v>
       </c>
       <c r="AN10" s="12">
-        <f t="shared" si="14"/>
-        <v>3819.8208610016072</v>
+        <f t="shared" si="15"/>
+        <v>3544.565657141603</v>
       </c>
       <c r="AO10" s="12">
-        <f t="shared" si="14"/>
-        <v>4137.7668177576697</v>
+        <f t="shared" si="15"/>
+        <v>3848.748853704672</v>
       </c>
       <c r="AP10" s="12">
-        <f t="shared" si="14"/>
-        <v>4476.6882688997794</v>
+        <f t="shared" si="15"/>
+        <v>4173.2194066441225</v>
       </c>
       <c r="AQ10" s="12">
-        <f t="shared" si="14"/>
-        <v>4837.8371170091577</v>
+        <f t="shared" si="15"/>
+        <v>4519.1948116407239</v>
       </c>
       <c r="AR10" s="12">
-        <f t="shared" si="14"/>
-        <v>5222.5359849105871</v>
+        <f t="shared" si="15"/>
+        <v>4887.9615642737326</v>
       </c>
       <c r="AS10" s="12">
-        <f t="shared" si="14"/>
-        <v>5632.1820766891233</v>
+        <f t="shared" si="15"/>
+        <v>5280.8789350204224</v>
       </c>
     </row>
     <row r="11" spans="1:200" x14ac:dyDescent="0.25">
@@ -3415,11 +3437,14 @@
       <c r="Q11" s="14">
         <v>-202</v>
       </c>
-      <c r="R11" s="48">
+      <c r="R11" s="14">
         <v>-182</v>
       </c>
-      <c r="S11" s="15">
+      <c r="S11" s="14">
         <v>-167</v>
+      </c>
+      <c r="T11" s="14">
+        <v>-202</v>
       </c>
       <c r="Y11" s="14">
         <f>44-388</f>
@@ -3461,10 +3486,10 @@
         <f>86-950</f>
         <v>-864</v>
       </c>
-      <c r="AI11" s="15">
+      <c r="AI11" s="14">
         <v>-750</v>
       </c>
-      <c r="AJ11" s="14">
+      <c r="AJ11" s="15">
         <v>0</v>
       </c>
       <c r="AK11" s="14">
@@ -3500,43 +3525,43 @@
         <v>63</v>
       </c>
       <c r="D12" s="14">
-        <f t="shared" ref="D12:M12" si="15">SUM(D10:D11)</f>
+        <f t="shared" ref="D12:M12" si="16">SUM(D10:D11)</f>
         <v>2098</v>
       </c>
       <c r="E12" s="14">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1977</v>
       </c>
       <c r="F12" s="14">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>469</v>
       </c>
       <c r="G12" s="14">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-1963</v>
       </c>
       <c r="H12" s="14">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2119</v>
       </c>
       <c r="I12" s="14">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1854</v>
       </c>
       <c r="J12" s="14">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>177</v>
       </c>
       <c r="K12" s="14">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>-1272</v>
       </c>
       <c r="L12" s="14">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1701</v>
       </c>
       <c r="M12" s="14">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1640</v>
       </c>
       <c r="N12" s="14">
@@ -3555,97 +3580,101 @@
         <f>SUM(Q10:Q11)</f>
         <v>1860</v>
       </c>
-      <c r="R12" s="48">
-        <f t="shared" ref="R12:S12" si="16">SUM(R10:R11)</f>
+      <c r="R12" s="14">
+        <f t="shared" ref="R12:S12" si="17">SUM(R10:R11)</f>
         <v>-40</v>
       </c>
-      <c r="S12" s="15">
-        <f t="shared" si="16"/>
+      <c r="S12" s="14">
+        <f t="shared" si="17"/>
         <v>-1003</v>
       </c>
+      <c r="T12" s="14">
+        <f t="shared" ref="T12" si="18">SUM(T10:T11)</f>
+        <v>1508</v>
+      </c>
       <c r="Y12" s="14">
-        <f t="shared" ref="Y12:AH12" si="17">SUM(Y10:Y11)</f>
+        <f t="shared" ref="Y12:AH12" si="19">SUM(Y10:Y11)</f>
         <v>2483</v>
       </c>
       <c r="Z12" s="14">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>2796</v>
       </c>
       <c r="AA12" s="14">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>3290</v>
       </c>
       <c r="AB12" s="14">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1561</v>
       </c>
       <c r="AC12" s="14">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>3122</v>
       </c>
       <c r="AD12" s="14">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>3330</v>
       </c>
       <c r="AE12" s="14">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>5494</v>
       </c>
       <c r="AF12" s="14">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>2582</v>
       </c>
       <c r="AG12" s="14">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>2878</v>
       </c>
       <c r="AH12" s="14">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1733</v>
       </c>
-      <c r="AI12" s="15">
-        <f t="shared" ref="AI12:AS12" si="18">SUM(AI10:AI11)</f>
+      <c r="AI12" s="14">
+        <f t="shared" ref="AI12:AS12" si="20">SUM(AI10:AI11)</f>
         <v>2149</v>
       </c>
-      <c r="AJ12" s="14">
-        <f t="shared" si="18"/>
-        <v>3026.6800000000012</v>
+      <c r="AJ12" s="15">
+        <f t="shared" si="20"/>
+        <v>2793.6100000000051</v>
       </c>
       <c r="AK12" s="14">
-        <f t="shared" si="18"/>
-        <v>3117.4804000000022</v>
+        <f t="shared" si="20"/>
+        <v>2877.4182999999994</v>
       </c>
       <c r="AL12" s="14">
-        <f t="shared" si="18"/>
-        <v>3242.1796159999994</v>
+        <f t="shared" si="20"/>
+        <v>2992.5150320000012</v>
       </c>
       <c r="AM12" s="14">
-        <f t="shared" si="18"/>
-        <v>3521.6655510400005</v>
+        <f t="shared" si="20"/>
+        <v>3259.5177378400031</v>
       </c>
       <c r="AN12" s="14">
-        <f t="shared" si="18"/>
-        <v>3819.8208610016072</v>
+        <f t="shared" si="20"/>
+        <v>3544.565657141603</v>
       </c>
       <c r="AO12" s="14">
-        <f t="shared" si="18"/>
-        <v>4137.7668177576697</v>
+        <f t="shared" si="20"/>
+        <v>3848.748853704672</v>
       </c>
       <c r="AP12" s="14">
-        <f t="shared" si="18"/>
-        <v>4476.6882688997794</v>
+        <f t="shared" si="20"/>
+        <v>4173.2194066441225</v>
       </c>
       <c r="AQ12" s="14">
-        <f t="shared" si="18"/>
-        <v>4837.8371170091577</v>
+        <f t="shared" si="20"/>
+        <v>4519.1948116407239</v>
       </c>
       <c r="AR12" s="14">
-        <f t="shared" si="18"/>
-        <v>5222.5359849105871</v>
+        <f t="shared" si="20"/>
+        <v>4887.9615642737326</v>
       </c>
       <c r="AS12" s="14">
-        <f t="shared" si="18"/>
-        <v>5632.1820766891233</v>
+        <f t="shared" si="20"/>
+        <v>5280.8789350204224</v>
       </c>
     </row>
     <row r="13" spans="1:200" x14ac:dyDescent="0.25">
@@ -3694,11 +3723,14 @@
       <c r="Q13" s="14">
         <v>-281</v>
       </c>
-      <c r="R13" s="48">
+      <c r="R13" s="14">
         <v>31</v>
       </c>
-      <c r="S13" s="15">
+      <c r="S13" s="14">
         <v>233</v>
+      </c>
+      <c r="T13" s="14">
+        <v>-335</v>
       </c>
       <c r="Y13" s="14">
         <v>-595</v>
@@ -3730,48 +3762,48 @@
       <c r="AH13" s="14">
         <v>-408</v>
       </c>
-      <c r="AI13" s="15">
+      <c r="AI13" s="14">
         <v>-379</v>
       </c>
-      <c r="AJ13" s="14">
+      <c r="AJ13" s="15">
         <f>AJ12*-0.2</f>
-        <v>-605.33600000000024</v>
+        <v>-558.722000000001</v>
       </c>
       <c r="AK13" s="14">
-        <f t="shared" ref="AK13:AS13" si="19">AK12*-0.2</f>
-        <v>-623.49608000000046</v>
+        <f t="shared" ref="AK13:AS13" si="21">AK12*-0.2</f>
+        <v>-575.48365999999987</v>
       </c>
       <c r="AL13" s="14">
-        <f t="shared" si="19"/>
-        <v>-648.43592319999993</v>
+        <f t="shared" si="21"/>
+        <v>-598.50300640000023</v>
       </c>
       <c r="AM13" s="14">
-        <f t="shared" si="19"/>
-        <v>-704.33311020800011</v>
+        <f t="shared" si="21"/>
+        <v>-651.9035475680007</v>
       </c>
       <c r="AN13" s="14">
-        <f t="shared" si="19"/>
-        <v>-763.96417220032151</v>
+        <f t="shared" si="21"/>
+        <v>-708.91313142832064</v>
       </c>
       <c r="AO13" s="14">
-        <f t="shared" si="19"/>
-        <v>-827.55336355153395</v>
+        <f t="shared" si="21"/>
+        <v>-769.74977074093442</v>
       </c>
       <c r="AP13" s="14">
-        <f t="shared" si="19"/>
-        <v>-895.33765377995587</v>
+        <f t="shared" si="21"/>
+        <v>-834.64388132882459</v>
       </c>
       <c r="AQ13" s="14">
-        <f t="shared" si="19"/>
-        <v>-967.56742340183155</v>
+        <f t="shared" si="21"/>
+        <v>-903.83896232814482</v>
       </c>
       <c r="AR13" s="14">
-        <f t="shared" si="19"/>
-        <v>-1044.5071969821174</v>
+        <f t="shared" si="21"/>
+        <v>-977.59231285474652</v>
       </c>
       <c r="AS13" s="14">
-        <f t="shared" si="19"/>
-        <v>-1126.4364153378247</v>
+        <f t="shared" si="21"/>
+        <v>-1056.1757870040844</v>
       </c>
     </row>
     <row r="14" spans="1:200" x14ac:dyDescent="0.25">
@@ -3779,43 +3811,43 @@
         <v>65</v>
       </c>
       <c r="D14" s="12">
-        <f t="shared" ref="D14:M14" si="20">SUM(D12:D13)</f>
+        <f t="shared" ref="D14:M14" si="22">SUM(D12:D13)</f>
         <v>1638</v>
       </c>
       <c r="E14" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>1416</v>
       </c>
       <c r="F14" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>270</v>
       </c>
       <c r="G14" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>-1392</v>
       </c>
       <c r="H14" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>1653</v>
       </c>
       <c r="I14" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>1411</v>
       </c>
       <c r="J14" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>124</v>
       </c>
       <c r="K14" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>-1011</v>
       </c>
       <c r="L14" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>1322</v>
       </c>
       <c r="M14" s="12">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>1271</v>
       </c>
       <c r="N14" s="12">
@@ -3834,717 +3866,721 @@
         <f>SUM(Q12:Q13)</f>
         <v>1579</v>
       </c>
-      <c r="R14" s="47">
-        <f t="shared" ref="R14:S14" si="21">SUM(R12:R13)</f>
+      <c r="R14" s="12">
+        <f t="shared" ref="R14:S14" si="23">SUM(R12:R13)</f>
         <v>-9</v>
       </c>
-      <c r="S14" s="13">
-        <f t="shared" si="21"/>
+      <c r="S14" s="12">
+        <f t="shared" si="23"/>
         <v>-770</v>
       </c>
+      <c r="T14" s="12">
+        <f t="shared" ref="T14" si="24">SUM(T12:T13)</f>
+        <v>1173</v>
+      </c>
       <c r="Y14" s="12">
-        <f t="shared" ref="Y14:AH14" si="22">SUM(Y12:Y13)</f>
+        <f t="shared" ref="Y14:AH14" si="25">SUM(Y12:Y13)</f>
         <v>1888</v>
       </c>
       <c r="Z14" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>2104</v>
       </c>
       <c r="AA14" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>2660</v>
       </c>
       <c r="AB14" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>1213</v>
       </c>
       <c r="AC14" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>2528</v>
       </c>
       <c r="AD14" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>2495</v>
       </c>
       <c r="AE14" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>4437</v>
       </c>
       <c r="AF14" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>1933</v>
       </c>
       <c r="AG14" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>2176</v>
       </c>
       <c r="AH14" s="12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>1325</v>
       </c>
-      <c r="AI14" s="13">
-        <f t="shared" ref="AI14:AS14" si="23">SUM(AI12:AI13)</f>
+      <c r="AI14" s="12">
+        <f t="shared" ref="AI14:AS14" si="26">SUM(AI12:AI13)</f>
         <v>1770</v>
       </c>
-      <c r="AJ14" s="12">
-        <f t="shared" si="23"/>
-        <v>2421.344000000001</v>
+      <c r="AJ14" s="13">
+        <f t="shared" si="26"/>
+        <v>2234.888000000004</v>
       </c>
       <c r="AK14" s="12">
-        <f t="shared" si="23"/>
-        <v>2493.9843200000018</v>
+        <f t="shared" si="26"/>
+        <v>2301.9346399999995</v>
       </c>
       <c r="AL14" s="12">
-        <f t="shared" si="23"/>
-        <v>2593.7436927999997</v>
+        <f t="shared" si="26"/>
+        <v>2394.0120256000009</v>
       </c>
       <c r="AM14" s="12">
-        <f t="shared" si="23"/>
-        <v>2817.3324408320004</v>
+        <f t="shared" si="26"/>
+        <v>2607.6141902720024</v>
       </c>
       <c r="AN14" s="12">
-        <f t="shared" si="23"/>
-        <v>3055.8566888012856</v>
+        <f t="shared" si="26"/>
+        <v>2835.6525257132826</v>
       </c>
       <c r="AO14" s="12">
-        <f t="shared" si="23"/>
-        <v>3310.2134542061358</v>
+        <f t="shared" si="26"/>
+        <v>3078.9990829637377</v>
       </c>
       <c r="AP14" s="12">
-        <f t="shared" si="23"/>
-        <v>3581.3506151198235</v>
+        <f t="shared" si="26"/>
+        <v>3338.5755253152979</v>
       </c>
       <c r="AQ14" s="12">
-        <f t="shared" si="23"/>
-        <v>3870.2696936073262</v>
+        <f t="shared" si="26"/>
+        <v>3615.3558493125793</v>
       </c>
       <c r="AR14" s="12">
-        <f t="shared" si="23"/>
-        <v>4178.0287879284697</v>
+        <f t="shared" si="26"/>
+        <v>3910.3692514189861</v>
       </c>
       <c r="AS14" s="12">
-        <f t="shared" si="23"/>
-        <v>4505.7456613512986</v>
+        <f t="shared" si="26"/>
+        <v>4224.7031480163378</v>
       </c>
       <c r="AT14" s="12">
         <f>AS14*(1+$AV$18)</f>
-        <v>4460.6882047377858</v>
+        <v>4182.4561165361747</v>
       </c>
       <c r="AU14" s="12">
-        <f t="shared" ref="AU14:DF14" si="24">AT14*(1+$AV$18)</f>
-        <v>4416.0813226904074</v>
+        <f t="shared" ref="AU14:DF14" si="27">AT14*(1+$AV$18)</f>
+        <v>4140.6315553708127</v>
       </c>
       <c r="AV14" s="12">
-        <f t="shared" si="24"/>
-        <v>4371.9205094635035</v>
+        <f t="shared" si="27"/>
+        <v>4099.2252398171049</v>
       </c>
       <c r="AW14" s="12">
-        <f t="shared" si="24"/>
-        <v>4328.2013043688685</v>
+        <f t="shared" si="27"/>
+        <v>4058.232987418934</v>
       </c>
       <c r="AX14" s="12">
-        <f t="shared" si="24"/>
-        <v>4284.91929132518</v>
+        <f t="shared" si="27"/>
+        <v>4017.6506575447447</v>
       </c>
       <c r="AY14" s="12">
-        <f t="shared" si="24"/>
-        <v>4242.0700984119285</v>
+        <f t="shared" si="27"/>
+        <v>3977.4741509692972</v>
       </c>
       <c r="AZ14" s="12">
-        <f t="shared" si="24"/>
-        <v>4199.6493974278092</v>
+        <f t="shared" si="27"/>
+        <v>3937.6994094596043</v>
       </c>
       <c r="BA14" s="12">
-        <f t="shared" si="24"/>
-        <v>4157.6529034535306</v>
+        <f t="shared" si="27"/>
+        <v>3898.3224153650081</v>
       </c>
       <c r="BB14" s="12">
-        <f t="shared" si="24"/>
-        <v>4116.0763744189953</v>
+        <f t="shared" si="27"/>
+        <v>3859.339191211358</v>
       </c>
       <c r="BC14" s="12">
-        <f t="shared" si="24"/>
-        <v>4074.9156106748055</v>
+        <f t="shared" si="27"/>
+        <v>3820.7457992992445</v>
       </c>
       <c r="BD14" s="12">
-        <f t="shared" si="24"/>
-        <v>4034.1664545680574</v>
+        <f t="shared" si="27"/>
+        <v>3782.5383413062518</v>
       </c>
       <c r="BE14" s="12">
-        <f t="shared" si="24"/>
-        <v>3993.8247900223769</v>
+        <f t="shared" si="27"/>
+        <v>3744.7129578931895</v>
       </c>
       <c r="BF14" s="12">
-        <f t="shared" si="24"/>
-        <v>3953.8865421221531</v>
+        <f t="shared" si="27"/>
+        <v>3707.2658283142578</v>
       </c>
       <c r="BG14" s="12">
-        <f t="shared" si="24"/>
-        <v>3914.3476767009315</v>
+        <f t="shared" si="27"/>
+        <v>3670.1931700311152</v>
       </c>
       <c r="BH14" s="12">
-        <f t="shared" si="24"/>
-        <v>3875.2041999339222</v>
+        <f t="shared" si="27"/>
+        <v>3633.4912383308042</v>
       </c>
       <c r="BI14" s="12">
-        <f t="shared" si="24"/>
-        <v>3836.4521579345828</v>
+        <f t="shared" si="27"/>
+        <v>3597.156325947496</v>
       </c>
       <c r="BJ14" s="12">
-        <f t="shared" si="24"/>
-        <v>3798.087636355237</v>
+        <f t="shared" si="27"/>
+        <v>3561.1847626880212</v>
       </c>
       <c r="BK14" s="12">
-        <f t="shared" si="24"/>
-        <v>3760.1067599916846</v>
+        <f t="shared" si="27"/>
+        <v>3525.572915061141</v>
       </c>
       <c r="BL14" s="12">
-        <f t="shared" si="24"/>
-        <v>3722.5056923917678</v>
+        <f t="shared" si="27"/>
+        <v>3490.3171859105296</v>
       </c>
       <c r="BM14" s="12">
-        <f t="shared" si="24"/>
-        <v>3685.2806354678501</v>
+        <f t="shared" si="27"/>
+        <v>3455.4140140514241</v>
       </c>
       <c r="BN14" s="12">
-        <f t="shared" si="24"/>
-        <v>3648.4278291131714</v>
+        <f t="shared" si="27"/>
+        <v>3420.8598739109098</v>
       </c>
       <c r="BO14" s="12">
-        <f t="shared" si="24"/>
-        <v>3611.9435508220395</v>
+        <f t="shared" si="27"/>
+        <v>3386.6512751718005</v>
       </c>
       <c r="BP14" s="12">
-        <f t="shared" si="24"/>
-        <v>3575.8241153138192</v>
+        <f t="shared" si="27"/>
+        <v>3352.7847624200826</v>
       </c>
       <c r="BQ14" s="12">
-        <f t="shared" si="24"/>
-        <v>3540.0658741606808</v>
+        <f t="shared" si="27"/>
+        <v>3319.2569147958816</v>
       </c>
       <c r="BR14" s="12">
-        <f t="shared" si="24"/>
-        <v>3504.6652154190738</v>
+        <f t="shared" si="27"/>
+        <v>3286.0643456479229</v>
       </c>
       <c r="BS14" s="12">
-        <f t="shared" si="24"/>
-        <v>3469.6185632648831</v>
+        <f t="shared" si="27"/>
+        <v>3253.2037021914434</v>
       </c>
       <c r="BT14" s="12">
-        <f t="shared" si="24"/>
-        <v>3434.9223776322342</v>
+        <f t="shared" si="27"/>
+        <v>3220.6716651695288</v>
       </c>
       <c r="BU14" s="12">
-        <f t="shared" si="24"/>
-        <v>3400.5731538559116</v>
+        <f t="shared" si="27"/>
+        <v>3188.4649485178334</v>
       </c>
       <c r="BV14" s="12">
-        <f t="shared" si="24"/>
-        <v>3366.5674223173523</v>
+        <f t="shared" si="27"/>
+        <v>3156.5802990326551</v>
       </c>
       <c r="BW14" s="12">
-        <f t="shared" si="24"/>
-        <v>3332.9017480941789</v>
+        <f t="shared" si="27"/>
+        <v>3125.0144960423286</v>
       </c>
       <c r="BX14" s="12">
-        <f t="shared" si="24"/>
-        <v>3299.5727306132371</v>
+        <f t="shared" si="27"/>
+        <v>3093.7643510819053</v>
       </c>
       <c r="BY14" s="12">
-        <f t="shared" si="24"/>
-        <v>3266.5770033071049</v>
+        <f t="shared" si="27"/>
+        <v>3062.826707571086</v>
       </c>
       <c r="BZ14" s="12">
-        <f t="shared" si="24"/>
-        <v>3233.9112332740337</v>
+        <f t="shared" si="27"/>
+        <v>3032.1984404953751</v>
       </c>
       <c r="CA14" s="12">
-        <f t="shared" si="24"/>
-        <v>3201.5721209412932</v>
+        <f t="shared" si="27"/>
+        <v>3001.8764560904215</v>
       </c>
       <c r="CB14" s="12">
-        <f t="shared" si="24"/>
-        <v>3169.55639973188</v>
+        <f t="shared" si="27"/>
+        <v>2971.8576915295171</v>
       </c>
       <c r="CC14" s="12">
-        <f t="shared" si="24"/>
-        <v>3137.8608357345611</v>
+        <f t="shared" si="27"/>
+        <v>2942.1391146142219</v>
       </c>
       <c r="CD14" s="12">
-        <f t="shared" si="24"/>
-        <v>3106.4822273772156</v>
+        <f t="shared" si="27"/>
+        <v>2912.7177234680794</v>
       </c>
       <c r="CE14" s="12">
-        <f t="shared" si="24"/>
-        <v>3075.4174051034433</v>
+        <f t="shared" si="27"/>
+        <v>2883.5905462333985</v>
       </c>
       <c r="CF14" s="12">
-        <f t="shared" si="24"/>
-        <v>3044.6632310524087</v>
+        <f t="shared" si="27"/>
+        <v>2854.7546407710647</v>
       </c>
       <c r="CG14" s="12">
-        <f t="shared" si="24"/>
-        <v>3014.2165987418848</v>
+        <f t="shared" si="27"/>
+        <v>2826.2070943633539</v>
       </c>
       <c r="CH14" s="12">
-        <f t="shared" si="24"/>
-        <v>2984.0744327544658</v>
+        <f t="shared" si="27"/>
+        <v>2797.9450234197202</v>
       </c>
       <c r="CI14" s="12">
-        <f t="shared" si="24"/>
-        <v>2954.2336884269212</v>
+        <f t="shared" si="27"/>
+        <v>2769.9655731855228</v>
       </c>
       <c r="CJ14" s="12">
-        <f t="shared" si="24"/>
-        <v>2924.6913515426518</v>
+        <f t="shared" si="27"/>
+        <v>2742.2659174536675</v>
       </c>
       <c r="CK14" s="12">
-        <f t="shared" si="24"/>
-        <v>2895.4444380272253</v>
+        <f t="shared" si="27"/>
+        <v>2714.8432582791306</v>
       </c>
       <c r="CL14" s="12">
-        <f t="shared" si="24"/>
-        <v>2866.4899936469528</v>
+        <f t="shared" si="27"/>
+        <v>2687.6948256963392</v>
       </c>
       <c r="CM14" s="12">
-        <f t="shared" si="24"/>
-        <v>2837.8250937104831</v>
+        <f t="shared" si="27"/>
+        <v>2660.8178774393759</v>
       </c>
       <c r="CN14" s="12">
-        <f t="shared" si="24"/>
-        <v>2809.4468427733782</v>
+        <f t="shared" si="27"/>
+        <v>2634.2096986649822</v>
       </c>
       <c r="CO14" s="12">
-        <f t="shared" si="24"/>
-        <v>2781.3523743456444</v>
+        <f t="shared" si="27"/>
+        <v>2607.8676016783324</v>
       </c>
       <c r="CP14" s="12">
-        <f t="shared" si="24"/>
-        <v>2753.5388506021882</v>
+        <f t="shared" si="27"/>
+        <v>2581.788925661549</v>
       </c>
       <c r="CQ14" s="12">
-        <f t="shared" si="24"/>
-        <v>2726.0034620961665</v>
+        <f t="shared" si="27"/>
+        <v>2555.9710364049333</v>
       </c>
       <c r="CR14" s="12">
-        <f t="shared" si="24"/>
-        <v>2698.743427475205</v>
+        <f t="shared" si="27"/>
+        <v>2530.411326040884</v>
       </c>
       <c r="CS14" s="12">
-        <f t="shared" si="24"/>
-        <v>2671.7559932004528</v>
+        <f t="shared" si="27"/>
+        <v>2505.107212780475</v>
       </c>
       <c r="CT14" s="12">
-        <f t="shared" si="24"/>
-        <v>2645.0384332684484</v>
+        <f t="shared" si="27"/>
+        <v>2480.0561406526704</v>
       </c>
       <c r="CU14" s="12">
-        <f t="shared" si="24"/>
-        <v>2618.5880489357637</v>
+        <f t="shared" si="27"/>
+        <v>2455.2555792461435</v>
       </c>
       <c r="CV14" s="12">
-        <f t="shared" si="24"/>
-        <v>2592.402168446406</v>
+        <f t="shared" si="27"/>
+        <v>2430.7030234536819</v>
       </c>
       <c r="CW14" s="12">
-        <f t="shared" si="24"/>
-        <v>2566.4781467619418</v>
+        <f t="shared" si="27"/>
+        <v>2406.3959932191451</v>
       </c>
       <c r="CX14" s="12">
-        <f t="shared" si="24"/>
-        <v>2540.8133652943225</v>
+        <f t="shared" si="27"/>
+        <v>2382.3320332869534</v>
       </c>
       <c r="CY14" s="12">
-        <f t="shared" si="24"/>
-        <v>2515.405231641379</v>
+        <f t="shared" si="27"/>
+        <v>2358.5087129540839</v>
       </c>
       <c r="CZ14" s="12">
-        <f t="shared" si="24"/>
-        <v>2490.2511793249651</v>
+        <f t="shared" si="27"/>
+        <v>2334.9236258245428</v>
       </c>
       <c r="DA14" s="12">
-        <f t="shared" si="24"/>
-        <v>2465.3486675317154</v>
+        <f t="shared" si="27"/>
+        <v>2311.5743895662972</v>
       </c>
       <c r="DB14" s="12">
-        <f t="shared" si="24"/>
-        <v>2440.6951808563981</v>
+        <f t="shared" si="27"/>
+        <v>2288.4586456706343</v>
       </c>
       <c r="DC14" s="12">
-        <f t="shared" si="24"/>
-        <v>2416.2882290478342</v>
+        <f t="shared" si="27"/>
+        <v>2265.5740592139277</v>
       </c>
       <c r="DD14" s="12">
-        <f t="shared" si="24"/>
-        <v>2392.1253467573561</v>
+        <f t="shared" si="27"/>
+        <v>2242.9183186217883</v>
       </c>
       <c r="DE14" s="12">
-        <f t="shared" si="24"/>
-        <v>2368.2040932897826</v>
+        <f t="shared" si="27"/>
+        <v>2220.4891354355705</v>
       </c>
       <c r="DF14" s="12">
-        <f t="shared" si="24"/>
-        <v>2344.5220523568846</v>
+        <f t="shared" si="27"/>
+        <v>2198.2842440812146</v>
       </c>
       <c r="DG14" s="12">
-        <f t="shared" ref="DG14:FR14" si="25">DF14*(1+$AV$18)</f>
-        <v>2321.0768318333157</v>
+        <f t="shared" ref="DG14:FR14" si="28">DF14*(1+$AV$18)</f>
+        <v>2176.3014016404027</v>
       </c>
       <c r="DH14" s="12">
-        <f t="shared" si="25"/>
-        <v>2297.8660635149827</v>
+        <f t="shared" si="28"/>
+        <v>2154.5383876239985</v>
       </c>
       <c r="DI14" s="12">
-        <f t="shared" si="25"/>
-        <v>2274.8874028798327</v>
+        <f t="shared" si="28"/>
+        <v>2132.9930037477584</v>
       </c>
       <c r="DJ14" s="12">
-        <f t="shared" si="25"/>
-        <v>2252.1385288510346</v>
+        <f t="shared" si="28"/>
+        <v>2111.663073710281</v>
       </c>
       <c r="DK14" s="12">
-        <f t="shared" si="25"/>
-        <v>2229.6171435625242</v>
+        <f t="shared" si="28"/>
+        <v>2090.5464429731783</v>
       </c>
       <c r="DL14" s="12">
-        <f t="shared" si="25"/>
-        <v>2207.3209721268991</v>
+        <f t="shared" si="28"/>
+        <v>2069.6409785434466</v>
       </c>
       <c r="DM14" s="12">
-        <f t="shared" si="25"/>
-        <v>2185.2477624056301</v>
+        <f t="shared" si="28"/>
+        <v>2048.9445687580123</v>
       </c>
       <c r="DN14" s="12">
-        <f t="shared" si="25"/>
-        <v>2163.3952847815735</v>
+        <f t="shared" si="28"/>
+        <v>2028.4551230704321</v>
       </c>
       <c r="DO14" s="12">
-        <f t="shared" si="25"/>
-        <v>2141.7613319337579</v>
+        <f t="shared" si="28"/>
+        <v>2008.1705718397277</v>
       </c>
       <c r="DP14" s="12">
-        <f t="shared" si="25"/>
-        <v>2120.3437186144201</v>
+        <f t="shared" si="28"/>
+        <v>1988.0888661213305</v>
       </c>
       <c r="DQ14" s="12">
-        <f t="shared" si="25"/>
-        <v>2099.140281428276</v>
+        <f t="shared" si="28"/>
+        <v>1968.2079774601173</v>
       </c>
       <c r="DR14" s="12">
-        <f t="shared" si="25"/>
-        <v>2078.148878613993</v>
+        <f t="shared" si="28"/>
+        <v>1948.5258976855162</v>
       </c>
       <c r="DS14" s="12">
-        <f t="shared" si="25"/>
-        <v>2057.367389827853</v>
+        <f t="shared" si="28"/>
+        <v>1929.0406387086609</v>
       </c>
       <c r="DT14" s="12">
-        <f t="shared" si="25"/>
-        <v>2036.7937159295745</v>
+        <f t="shared" si="28"/>
+        <v>1909.7502323215742</v>
       </c>
       <c r="DU14" s="12">
-        <f t="shared" si="25"/>
-        <v>2016.4257787702788</v>
+        <f t="shared" si="28"/>
+        <v>1890.6527299983584</v>
       </c>
       <c r="DV14" s="12">
-        <f t="shared" si="25"/>
-        <v>1996.261520982576</v>
+        <f t="shared" si="28"/>
+        <v>1871.7462026983749</v>
       </c>
       <c r="DW14" s="12">
-        <f t="shared" si="25"/>
-        <v>1976.2989057727502</v>
+        <f t="shared" si="28"/>
+        <v>1853.028740671391</v>
       </c>
       <c r="DX14" s="12">
-        <f t="shared" si="25"/>
-        <v>1956.5359167150227</v>
+        <f t="shared" si="28"/>
+        <v>1834.498453264677</v>
       </c>
       <c r="DY14" s="12">
-        <f t="shared" si="25"/>
-        <v>1936.9705575478724</v>
+        <f t="shared" si="28"/>
+        <v>1816.1534687320302</v>
       </c>
       <c r="DZ14" s="12">
-        <f t="shared" si="25"/>
-        <v>1917.6008519723937</v>
+        <f t="shared" si="28"/>
+        <v>1797.99193404471</v>
       </c>
       <c r="EA14" s="12">
-        <f t="shared" si="25"/>
-        <v>1898.4248434526696</v>
+        <f t="shared" si="28"/>
+        <v>1780.0120147042628</v>
       </c>
       <c r="EB14" s="12">
-        <f t="shared" si="25"/>
-        <v>1879.4405950181429</v>
+        <f t="shared" si="28"/>
+        <v>1762.2118945572201</v>
       </c>
       <c r="EC14" s="12">
-        <f t="shared" si="25"/>
-        <v>1860.6461890679614</v>
+        <f t="shared" si="28"/>
+        <v>1744.5897756116478</v>
       </c>
       <c r="ED14" s="12">
-        <f t="shared" si="25"/>
-        <v>1842.0397271772817</v>
+        <f t="shared" si="28"/>
+        <v>1727.1438778555314</v>
       </c>
       <c r="EE14" s="12">
-        <f t="shared" si="25"/>
-        <v>1823.6193299055089</v>
+        <f t="shared" si="28"/>
+        <v>1709.872439076976</v>
       </c>
       <c r="EF14" s="12">
-        <f t="shared" si="25"/>
-        <v>1805.3831366064539</v>
+        <f t="shared" si="28"/>
+        <v>1692.7737146862062</v>
       </c>
       <c r="EG14" s="12">
-        <f t="shared" si="25"/>
-        <v>1787.3293052403894</v>
+        <f t="shared" si="28"/>
+        <v>1675.8459775393442</v>
       </c>
       <c r="EH14" s="12">
-        <f t="shared" si="25"/>
-        <v>1769.4560121879856</v>
+        <f t="shared" si="28"/>
+        <v>1659.0875177639507</v>
       </c>
       <c r="EI14" s="12">
-        <f t="shared" si="25"/>
-        <v>1751.7614520661057</v>
+        <f t="shared" si="28"/>
+        <v>1642.4966425863113</v>
       </c>
       <c r="EJ14" s="12">
-        <f t="shared" si="25"/>
-        <v>1734.2438375454446</v>
+        <f t="shared" si="28"/>
+        <v>1626.0716761604481</v>
       </c>
       <c r="EK14" s="12">
-        <f t="shared" si="25"/>
-        <v>1716.9013991699901</v>
+        <f t="shared" si="28"/>
+        <v>1609.8109593988436</v>
       </c>
       <c r="EL14" s="12">
-        <f t="shared" si="25"/>
-        <v>1699.7323851782901</v>
+        <f t="shared" si="28"/>
+        <v>1593.7128498048551</v>
       </c>
       <c r="EM14" s="12">
-        <f t="shared" si="25"/>
-        <v>1682.7350613265071</v>
+        <f t="shared" si="28"/>
+        <v>1577.7757213068064</v>
       </c>
       <c r="EN14" s="12">
-        <f t="shared" si="25"/>
-        <v>1665.9077107132421</v>
+        <f t="shared" si="28"/>
+        <v>1561.9979640937383</v>
       </c>
       <c r="EO14" s="12">
-        <f t="shared" si="25"/>
-        <v>1649.2486336061097</v>
+        <f t="shared" si="28"/>
+        <v>1546.377984452801</v>
       </c>
       <c r="EP14" s="12">
-        <f t="shared" si="25"/>
-        <v>1632.7561472700486</v>
+        <f t="shared" si="28"/>
+        <v>1530.9142046082729</v>
       </c>
       <c r="EQ14" s="12">
-        <f t="shared" si="25"/>
-        <v>1616.428585797348</v>
+        <f t="shared" si="28"/>
+        <v>1515.6050625621901</v>
       </c>
       <c r="ER14" s="12">
-        <f t="shared" si="25"/>
-        <v>1600.2642999393745</v>
+        <f t="shared" si="28"/>
+        <v>1500.4490119365682</v>
       </c>
       <c r="ES14" s="12">
-        <f t="shared" si="25"/>
-        <v>1584.2616569399806</v>
+        <f t="shared" si="28"/>
+        <v>1485.4445218172025</v>
       </c>
       <c r="ET14" s="12">
-        <f t="shared" si="25"/>
-        <v>1568.4190403705809</v>
+        <f t="shared" si="28"/>
+        <v>1470.5900765990305</v>
       </c>
       <c r="EU14" s="12">
-        <f t="shared" si="25"/>
-        <v>1552.7348499668751</v>
+        <f t="shared" si="28"/>
+        <v>1455.8841758330402</v>
       </c>
       <c r="EV14" s="12">
-        <f t="shared" si="25"/>
-        <v>1537.2075014672064</v>
+        <f t="shared" si="28"/>
+        <v>1441.3253340747099</v>
       </c>
       <c r="EW14" s="12">
-        <f t="shared" si="25"/>
-        <v>1521.8354264525342</v>
+        <f t="shared" si="28"/>
+        <v>1426.9120807339627</v>
       </c>
       <c r="EX14" s="12">
-        <f t="shared" si="25"/>
-        <v>1506.6170721880089</v>
+        <f t="shared" si="28"/>
+        <v>1412.642959926623</v>
       </c>
       <c r="EY14" s="12">
-        <f t="shared" si="25"/>
-        <v>1491.5509014661288</v>
+        <f t="shared" si="28"/>
+        <v>1398.5165303273568</v>
       </c>
       <c r="EZ14" s="12">
-        <f t="shared" si="25"/>
-        <v>1476.6353924514676</v>
+        <f t="shared" si="28"/>
+        <v>1384.5313650240832</v>
       </c>
       <c r="FA14" s="12">
-        <f t="shared" si="25"/>
-        <v>1461.8690385269529</v>
+        <f t="shared" si="28"/>
+        <v>1370.6860513738425</v>
       </c>
       <c r="FB14" s="12">
-        <f t="shared" si="25"/>
-        <v>1447.2503481416834</v>
+        <f t="shared" si="28"/>
+        <v>1356.9791908601039</v>
       </c>
       <c r="FC14" s="12">
-        <f t="shared" si="25"/>
-        <v>1432.7778446602665</v>
+        <f t="shared" si="28"/>
+        <v>1343.4093989515029</v>
       </c>
       <c r="FD14" s="12">
-        <f t="shared" si="25"/>
-        <v>1418.4500662136638</v>
+        <f t="shared" si="28"/>
+        <v>1329.9753049619878</v>
       </c>
       <c r="FE14" s="12">
-        <f t="shared" si="25"/>
-        <v>1404.2655655515273</v>
+        <f t="shared" si="28"/>
+        <v>1316.6755519123678</v>
       </c>
       <c r="FF14" s="12">
-        <f t="shared" si="25"/>
-        <v>1390.222909896012</v>
+        <f t="shared" si="28"/>
+        <v>1303.5087963932442</v>
       </c>
       <c r="FG14" s="12">
-        <f t="shared" si="25"/>
-        <v>1376.3206807970519</v>
+        <f t="shared" si="28"/>
+        <v>1290.4737084293117</v>
       </c>
       <c r="FH14" s="12">
-        <f t="shared" si="25"/>
-        <v>1362.5574739890812</v>
+        <f t="shared" si="28"/>
+        <v>1277.5689713450186</v>
       </c>
       <c r="FI14" s="12">
-        <f t="shared" si="25"/>
-        <v>1348.9318992491903</v>
+        <f t="shared" si="28"/>
+        <v>1264.7932816315683</v>
       </c>
       <c r="FJ14" s="12">
-        <f t="shared" si="25"/>
-        <v>1335.4425802566984</v>
+        <f t="shared" si="28"/>
+        <v>1252.1453488152526</v>
       </c>
       <c r="FK14" s="12">
-        <f t="shared" si="25"/>
-        <v>1322.0881544541314</v>
+        <f t="shared" si="28"/>
+        <v>1239.6238953271002</v>
       </c>
       <c r="FL14" s="12">
-        <f t="shared" si="25"/>
-        <v>1308.8672729095902</v>
+        <f t="shared" si="28"/>
+        <v>1227.2276563738292</v>
       </c>
       <c r="FM14" s="12">
-        <f t="shared" si="25"/>
-        <v>1295.7786001804943</v>
+        <f t="shared" si="28"/>
+        <v>1214.9553798100908</v>
       </c>
       <c r="FN14" s="12">
-        <f t="shared" si="25"/>
-        <v>1282.8208141786893</v>
+        <f t="shared" si="28"/>
+        <v>1202.8058260119899</v>
       </c>
       <c r="FO14" s="12">
-        <f t="shared" si="25"/>
-        <v>1269.9926060369023</v>
+        <f t="shared" si="28"/>
+        <v>1190.77776775187</v>
       </c>
       <c r="FP14" s="12">
-        <f t="shared" si="25"/>
-        <v>1257.2926799765332</v>
+        <f t="shared" si="28"/>
+        <v>1178.8699900743513</v>
       </c>
       <c r="FQ14" s="12">
-        <f t="shared" si="25"/>
-        <v>1244.7197531767679</v>
+        <f t="shared" si="28"/>
+        <v>1167.0812901736078</v>
       </c>
       <c r="FR14" s="12">
-        <f t="shared" si="25"/>
-        <v>1232.2725556450002</v>
+        <f t="shared" si="28"/>
+        <v>1155.4104772718717</v>
       </c>
       <c r="FS14" s="12">
-        <f t="shared" ref="FS14:GR14" si="26">FR14*(1+$AV$18)</f>
-        <v>1219.9498300885502</v>
+        <f t="shared" ref="FS14:GR14" si="29">FR14*(1+$AV$18)</f>
+        <v>1143.8563724991529</v>
       </c>
       <c r="FT14" s="12">
-        <f t="shared" si="26"/>
-        <v>1207.7503317876647</v>
+        <f t="shared" si="29"/>
+        <v>1132.4178087741614</v>
       </c>
       <c r="FU14" s="12">
-        <f t="shared" si="26"/>
-        <v>1195.6728284697881</v>
+        <f t="shared" si="29"/>
+        <v>1121.0936306864198</v>
       </c>
       <c r="FV14" s="12">
-        <f t="shared" si="26"/>
-        <v>1183.7161001850902</v>
+        <f t="shared" si="29"/>
+        <v>1109.8826943795557</v>
       </c>
       <c r="FW14" s="12">
-        <f t="shared" si="26"/>
-        <v>1171.8789391832393</v>
+        <f t="shared" si="29"/>
+        <v>1098.7838674357602</v>
       </c>
       <c r="FX14" s="12">
-        <f t="shared" si="26"/>
-        <v>1160.1601497914069</v>
+        <f t="shared" si="29"/>
+        <v>1087.7960287614026</v>
       </c>
       <c r="FY14" s="12">
-        <f t="shared" si="26"/>
-        <v>1148.5585482934928</v>
+        <f t="shared" si="29"/>
+        <v>1076.9180684737885</v>
       </c>
       <c r="FZ14" s="12">
-        <f t="shared" si="26"/>
-        <v>1137.0729628105578</v>
+        <f t="shared" si="29"/>
+        <v>1066.1488877890506</v>
       </c>
       <c r="GA14" s="12">
-        <f t="shared" si="26"/>
-        <v>1125.7022331824521</v>
+        <f t="shared" si="29"/>
+        <v>1055.4873989111602</v>
       </c>
       <c r="GB14" s="12">
-        <f t="shared" si="26"/>
-        <v>1114.4452108506275</v>
+        <f t="shared" si="29"/>
+        <v>1044.9325249220485</v>
       </c>
       <c r="GC14" s="12">
-        <f t="shared" si="26"/>
-        <v>1103.3007587421212</v>
+        <f t="shared" si="29"/>
+        <v>1034.4831996728281</v>
       </c>
       <c r="GD14" s="12">
-        <f t="shared" si="26"/>
-        <v>1092.2677511546999</v>
+        <f t="shared" si="29"/>
+        <v>1024.1383676760997</v>
       </c>
       <c r="GE14" s="12">
-        <f t="shared" si="26"/>
-        <v>1081.345073643153</v>
+        <f t="shared" si="29"/>
+        <v>1013.8969839993388</v>
       </c>
       <c r="GF14" s="12">
-        <f t="shared" si="26"/>
-        <v>1070.5316229067214</v>
+        <f t="shared" si="29"/>
+        <v>1003.7580141593454</v>
       </c>
       <c r="GG14" s="12">
-        <f t="shared" si="26"/>
-        <v>1059.8263066776542</v>
+        <f t="shared" si="29"/>
+        <v>993.72043401775193</v>
       </c>
       <c r="GH14" s="12">
-        <f t="shared" si="26"/>
-        <v>1049.2280436108776</v>
+        <f t="shared" si="29"/>
+        <v>983.78322967757435</v>
       </c>
       <c r="GI14" s="12">
-        <f t="shared" si="26"/>
-        <v>1038.7357631747689</v>
+        <f t="shared" si="29"/>
+        <v>973.94539738079857</v>
       </c>
       <c r="GJ14" s="12">
-        <f t="shared" si="26"/>
-        <v>1028.3484055430213</v>
+        <f t="shared" si="29"/>
+        <v>964.20594340699063</v>
       </c>
       <c r="GK14" s="12">
-        <f t="shared" si="26"/>
-        <v>1018.0649214875911</v>
+        <f t="shared" si="29"/>
+        <v>954.56388397292073</v>
       </c>
       <c r="GL14" s="12">
-        <f t="shared" si="26"/>
-        <v>1007.8842722727152</v>
+        <f t="shared" si="29"/>
+        <v>945.0182451331915</v>
       </c>
       <c r="GM14" s="12">
-        <f t="shared" si="26"/>
-        <v>997.80542954998805</v>
+        <f t="shared" si="29"/>
+        <v>935.5680626818596</v>
       </c>
       <c r="GN14" s="12">
-        <f t="shared" si="26"/>
-        <v>987.82737525448817</v>
+        <f t="shared" si="29"/>
+        <v>926.21238205504096</v>
       </c>
       <c r="GO14" s="12">
-        <f t="shared" si="26"/>
-        <v>977.94910150194323</v>
+        <f t="shared" si="29"/>
+        <v>916.95025823449055</v>
       </c>
       <c r="GP14" s="12">
-        <f t="shared" si="26"/>
-        <v>968.16961048692383</v>
+        <f t="shared" si="29"/>
+        <v>907.78075565214567</v>
       </c>
       <c r="GQ14" s="12">
-        <f t="shared" si="26"/>
-        <v>958.48791438205456</v>
+        <f t="shared" si="29"/>
+        <v>898.70294809562415</v>
       </c>
       <c r="GR14" s="12">
-        <f t="shared" si="26"/>
-        <v>948.903035238234</v>
+        <f t="shared" si="29"/>
+        <v>889.71591861466788</v>
       </c>
     </row>
     <row r="15" spans="1:200" x14ac:dyDescent="0.25">
@@ -4593,10 +4629,13 @@
       <c r="Q15" s="2">
         <v>571.70000000000005</v>
       </c>
-      <c r="R15" s="45">
+      <c r="R15" s="2">
         <v>571.70000000000005</v>
       </c>
-      <c r="S15" s="4">
+      <c r="S15" s="2">
+        <v>571.70000000000005</v>
+      </c>
+      <c r="T15" s="2">
         <v>571.70000000000005</v>
       </c>
       <c r="Y15" s="2">
@@ -4629,10 +4668,10 @@
       <c r="AH15" s="2">
         <v>571.70000000000005</v>
       </c>
-      <c r="AI15" s="4">
+      <c r="AI15" s="2">
         <v>571.70000000000005</v>
       </c>
-      <c r="AJ15" s="2">
+      <c r="AJ15" s="4">
         <v>571.70000000000005</v>
       </c>
       <c r="AK15" s="2">
@@ -4668,51 +4707,51 @@
         <v>67</v>
       </c>
       <c r="D16" s="19">
-        <f t="shared" ref="D16:O16" si="27">D14/D15</f>
+        <f t="shared" ref="D16:O16" si="30">D14/D15</f>
         <v>2.8656403079076278</v>
       </c>
       <c r="E16" s="19">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>2.4772568229531138</v>
       </c>
       <c r="F16" s="19">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>0.47235829251224631</v>
       </c>
       <c r="G16" s="19">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>-2.4352694191742477</v>
       </c>
       <c r="H16" s="19">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>2.891882435269419</v>
       </c>
       <c r="I16" s="19">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>2.4685094471658502</v>
       </c>
       <c r="J16" s="19">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>0.21693491952414276</v>
       </c>
       <c r="K16" s="19">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>-1.7687193841847446</v>
       </c>
       <c r="L16" s="19">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>2.3128061581525543</v>
       </c>
       <c r="M16" s="19">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>2.223582925122463</v>
       </c>
       <c r="N16" s="19">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>-0.26587370998775578</v>
       </c>
       <c r="O16" s="19">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>-1.9538219345810739</v>
       </c>
       <c r="P16" s="19">
@@ -4723,98 +4762,102 @@
         <f>Q14/Q15</f>
         <v>2.7619380794122788</v>
       </c>
-      <c r="R16" s="49">
-        <f t="shared" ref="R16:S16" si="28">R14/R15</f>
+      <c r="R16" s="19">
+        <f t="shared" ref="R16:S16" si="31">R14/R15</f>
         <v>-1.5742522301906592E-2</v>
       </c>
-      <c r="S16" s="24">
-        <f t="shared" si="28"/>
+      <c r="S16" s="19">
+        <f t="shared" si="31"/>
         <v>-1.3468602413853419</v>
+      </c>
+      <c r="T16" s="19">
+        <f t="shared" ref="T16" si="32">T14/T15</f>
+        <v>2.0517754066818261</v>
       </c>
       <c r="X16" s="19"/>
       <c r="Y16" s="19">
-        <f t="shared" ref="Y16:AH16" si="29">Y14/Y15</f>
+        <f t="shared" ref="Y16:AH16" si="33">Y14/Y15</f>
         <v>3.3024313451110721</v>
       </c>
       <c r="Z16" s="19">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>3.6802518803568303</v>
       </c>
       <c r="AA16" s="19">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>4.6527899247857265</v>
       </c>
       <c r="AB16" s="19">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>2.1217421724680774</v>
       </c>
       <c r="AC16" s="19">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>4.4218995976910964</v>
       </c>
       <c r="AD16" s="19">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>4.3641770159174387</v>
       </c>
       <c r="AE16" s="19">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>7.7610634948399504</v>
       </c>
       <c r="AF16" s="19">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>3.3811439566206047</v>
       </c>
       <c r="AG16" s="19">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>3.806192058772083</v>
       </c>
       <c r="AH16" s="19">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>2.3176491166695818</v>
       </c>
-      <c r="AI16" s="24">
-        <f t="shared" ref="AI16:AS16" si="30">AI14/AI15</f>
+      <c r="AI16" s="19">
+        <f t="shared" ref="AI16:AS16" si="34">AI14/AI15</f>
         <v>3.0960293860416299</v>
       </c>
-      <c r="AJ16" s="19">
-        <f t="shared" si="30"/>
-        <v>4.2353402133986373</v>
+      <c r="AJ16" s="24">
+        <f t="shared" si="34"/>
+        <v>3.9091971313626095</v>
       </c>
       <c r="AK16" s="19">
-        <f t="shared" si="30"/>
-        <v>4.3624004198005979</v>
+        <f t="shared" si="34"/>
+        <v>4.0264730453034794</v>
       </c>
       <c r="AL16" s="19">
-        <f t="shared" si="30"/>
-        <v>4.5368964365926177</v>
+        <f t="shared" si="34"/>
+        <v>4.1875319671156213</v>
       </c>
       <c r="AM16" s="19">
-        <f t="shared" si="30"/>
-        <v>4.9279909757425227</v>
+        <f t="shared" si="34"/>
+        <v>4.5611582827916779</v>
       </c>
       <c r="AN16" s="19">
-        <f t="shared" si="30"/>
-        <v>5.3452102305427411</v>
+        <f t="shared" si="34"/>
+        <v>4.9600359029443455</v>
       </c>
       <c r="AO16" s="19">
-        <f t="shared" si="30"/>
-        <v>5.7901232363234838</v>
+        <f t="shared" si="34"/>
+        <v>5.3856901923451765</v>
       </c>
       <c r="AP16" s="19">
-        <f t="shared" si="30"/>
-        <v>6.2643879921634129</v>
+        <f t="shared" si="34"/>
+        <v>5.8397332959861776</v>
       </c>
       <c r="AQ16" s="19">
-        <f t="shared" si="30"/>
-        <v>6.769756329556281</v>
+        <f t="shared" si="34"/>
+        <v>6.3238688985701925</v>
       </c>
       <c r="AR16" s="19">
-        <f t="shared" si="30"/>
-        <v>7.3080790413301893</v>
+        <f t="shared" si="34"/>
+        <v>6.8398972387947978</v>
       </c>
       <c r="AS16" s="19">
-        <f t="shared" si="30"/>
-        <v>7.8813112845046325</v>
+        <f t="shared" si="34"/>
+        <v>7.3897203918424657</v>
       </c>
     </row>
     <row r="17" spans="3:48" x14ac:dyDescent="0.25">
@@ -4825,8 +4868,8 @@
       <c r="I17" s="9"/>
       <c r="J17" s="9"/>
       <c r="K17" s="9"/>
-      <c r="AI17" s="8"/>
-      <c r="AJ17" s="9"/>
+      <c r="AI17" s="9"/>
+      <c r="AJ17" s="8"/>
       <c r="AK17" s="9"/>
       <c r="AL17" s="9"/>
       <c r="AM17" s="9"/>
@@ -4852,131 +4895,147 @@
       <c r="F18" s="19"/>
       <c r="G18" s="19"/>
       <c r="H18" s="18">
-        <f t="shared" ref="H18:P18" si="31">(H4-D4)/D4</f>
+        <f t="shared" ref="H18:P18" si="35">(H4-D4)/D4</f>
         <v>9.4485176920624803E-2</v>
       </c>
       <c r="I18" s="18">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>7.4974670719351572E-2</v>
       </c>
       <c r="J18" s="18">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>-0.13878420448959528</v>
       </c>
       <c r="K18" s="18">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>-0.16883994977301264</v>
       </c>
       <c r="L18" s="18">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>-0.14259917283159551</v>
       </c>
       <c r="M18" s="18">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>-9.1069745523091425E-2</v>
       </c>
       <c r="N18" s="18">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>-7.3535007610350075E-2</v>
       </c>
       <c r="O18" s="18">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>-1.6385822196397445E-2</v>
       </c>
       <c r="P18" s="18">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>-1.0190909708539982E-3</v>
       </c>
       <c r="Q18" s="18">
         <f>(Q4-M4)/M4</f>
         <v>-9.9157485418016854E-3</v>
       </c>
-      <c r="R18" s="50">
-        <f t="shared" ref="R18:S18" si="32">(R4-N4)/N4</f>
+      <c r="R18" s="18">
+        <f t="shared" ref="R18:S18" si="36">(R4-N4)/N4</f>
         <v>-5.4933771434438852E-2</v>
       </c>
-      <c r="S18" s="25">
-        <f t="shared" si="32"/>
+      <c r="S18" s="18">
+        <f t="shared" si="36"/>
         <v>-0.12228260869565218</v>
       </c>
+      <c r="T18" s="18">
+        <f t="shared" ref="T18" si="37">(T4-P4)/P4</f>
+        <v>-5.0462459194776932E-2</v>
+      </c>
+      <c r="U18" s="18">
+        <f t="shared" ref="U18" si="38">(U4-Q4)/Q4</f>
+        <v>-1</v>
+      </c>
+      <c r="V18" s="18">
+        <f t="shared" ref="V18" si="39">(V4-R4)/R4</f>
+        <v>-1</v>
+      </c>
+      <c r="W18" s="18">
+        <f t="shared" ref="W18" si="40">(W4-S4)/S4</f>
+        <v>-1</v>
+      </c>
       <c r="Z18" s="18">
-        <f t="shared" ref="Z18:AG18" si="33">(Z4-Y4)/Y4</f>
+        <f t="shared" ref="Z18:AG18" si="41">(Z4-Y4)/Y4</f>
         <v>-5.1976776333978432E-3</v>
       </c>
       <c r="AA18" s="18">
-        <f t="shared" si="33"/>
+        <f t="shared" si="41"/>
         <v>9.482519037296426E-2</v>
       </c>
       <c r="AB18" s="18">
-        <f t="shared" si="33"/>
+        <f t="shared" si="41"/>
         <v>4.2925318576432961E-2</v>
       </c>
       <c r="AC18" s="18">
-        <f t="shared" si="33"/>
+        <f t="shared" si="41"/>
         <v>2.901302178410612E-2</v>
       </c>
       <c r="AD18" s="18">
-        <f t="shared" si="33"/>
+        <f t="shared" si="41"/>
         <v>-7.9002767462213498E-3</v>
       </c>
       <c r="AE18" s="18">
-        <f t="shared" si="33"/>
+        <f t="shared" si="41"/>
         <v>0.12197506139284267</v>
       </c>
       <c r="AF18" s="18">
-        <f t="shared" si="33"/>
+        <f t="shared" si="41"/>
         <v>0.14828194394271021</v>
       </c>
       <c r="AG18" s="18">
-        <f t="shared" si="33"/>
+        <f t="shared" si="41"/>
         <v>-1.4360530747450822E-2</v>
       </c>
       <c r="AH18" s="18">
         <f>(AH4-AG4)/AG4</f>
         <v>-9.2168753872439502E-2</v>
       </c>
-      <c r="AI18" s="25">
-        <f t="shared" ref="AI18:AS18" si="34">(AI4-AH4)/AH4</f>
+      <c r="AI18" s="18">
+        <f t="shared" ref="AI18:AS18" si="42">(AI4-AH4)/AH4</f>
         <v>-3.5944738583719389E-2</v>
       </c>
-      <c r="AJ18" s="18">
-        <f t="shared" si="34"/>
+      <c r="AJ18" s="25">
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="AK18" s="18">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>2.9999999999999964E-2</v>
       </c>
       <c r="AL18" s="18">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>4.0000000000000022E-2</v>
       </c>
       <c r="AM18" s="18">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>5.0000000000000093E-2</v>
       </c>
       <c r="AN18" s="18">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>5.0000000000000072E-2</v>
       </c>
       <c r="AO18" s="18">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>5.0000000000000107E-2</v>
       </c>
       <c r="AP18" s="18">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>5.0000000000000072E-2</v>
       </c>
       <c r="AQ18" s="18">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>5.0000000000000037E-2</v>
       </c>
       <c r="AR18" s="18">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>5.0000000000000086E-2</v>
       </c>
       <c r="AS18" s="18">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>5.0000000000000031E-2</v>
       </c>
       <c r="AU18" s="2" t="s">
@@ -5032,18 +5091,24 @@
       <c r="Q19" s="18">
         <v>0.05</v>
       </c>
-      <c r="R19" s="50">
+      <c r="R19" s="18">
         <v>0</v>
       </c>
-      <c r="S19" s="25">
+      <c r="S19" s="18">
         <v>-0.03</v>
       </c>
+      <c r="T19" s="18">
+        <v>0.02</v>
+      </c>
+      <c r="U19" s="18"/>
+      <c r="V19" s="18"/>
+      <c r="W19" s="18"/>
       <c r="AU19" s="26" t="s">
         <v>120</v>
       </c>
       <c r="AV19" s="28">
         <f>NPV(AV17,AJ14:GR14)</f>
-        <v>43990.833530342199</v>
+        <v>41069.86518720923</v>
       </c>
     </row>
     <row r="20" spans="3:48" x14ac:dyDescent="0.25">
@@ -5051,152 +5116,168 @@
         <v>68</v>
       </c>
       <c r="D20" s="20">
-        <f t="shared" ref="D20:S20" si="35">D6/D4</f>
+        <f t="shared" ref="D20:S20" si="43">D6/D4</f>
         <v>0.31743704175964299</v>
       </c>
       <c r="E20" s="20">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v>0.33004052684903751</v>
       </c>
       <c r="F20" s="20">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v>0.25831558250040965</v>
       </c>
       <c r="G20" s="20">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v>0.12247657683763161</v>
       </c>
       <c r="H20" s="20">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v>0.33144987475971338</v>
       </c>
       <c r="I20" s="20">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v>0.32669651272384542</v>
       </c>
       <c r="J20" s="20">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v>0.29670852359208522</v>
       </c>
       <c r="K20" s="20">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v>0.20557815223707146</v>
       </c>
       <c r="L20" s="20">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v>0.33738705075073033</v>
       </c>
       <c r="M20" s="20">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v>0.33661697990926764</v>
       </c>
       <c r="N20" s="20">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v>0.25998562480747511</v>
       </c>
       <c r="O20" s="20">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v>0.18986294896030245</v>
       </c>
       <c r="P20" s="20">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v>0.30821545157780195</v>
       </c>
       <c r="Q20" s="20">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v>0.33880997578058519</v>
       </c>
-      <c r="R20" s="51">
-        <f t="shared" si="35"/>
+      <c r="R20" s="20">
+        <f t="shared" si="43"/>
         <v>0.28498478922207737</v>
       </c>
-      <c r="S20" s="21">
-        <f t="shared" si="35"/>
+      <c r="S20" s="20">
+        <f t="shared" si="43"/>
         <v>0.23812087764167453</v>
       </c>
+      <c r="T20" s="20">
+        <f t="shared" ref="T20:W20" si="44">T6/T4</f>
+        <v>0.32552642887838418</v>
+      </c>
+      <c r="U20" s="20" t="e">
+        <f t="shared" si="44"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V20" s="20" t="e">
+        <f t="shared" si="44"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W20" s="20" t="e">
+        <f t="shared" si="44"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="Y20" s="20">
-        <f t="shared" ref="Y20:AS20" si="36">Y6/Y4</f>
+        <f t="shared" ref="Y20:AS20" si="45">Y6/Y4</f>
         <v>0.28128283107547691</v>
       </c>
       <c r="Z20" s="20">
-        <f t="shared" si="36"/>
+        <f t="shared" si="45"/>
         <v>0.30837641042743597</v>
       </c>
       <c r="AA20" s="20">
-        <f t="shared" si="36"/>
+        <f t="shared" si="45"/>
         <v>0.29121185967406205</v>
       </c>
       <c r="AB20" s="20">
-        <f t="shared" si="36"/>
+        <f t="shared" si="45"/>
         <v>0.25561640501399535</v>
       </c>
       <c r="AC20" s="20">
-        <f t="shared" si="36"/>
+        <f t="shared" si="45"/>
         <v>0.29635499207606975</v>
       </c>
       <c r="AD20" s="20">
-        <f t="shared" si="36"/>
+        <f t="shared" si="45"/>
         <v>0.29983549102353196</v>
       </c>
       <c r="AE20" s="20">
-        <f t="shared" si="36"/>
+        <f t="shared" si="45"/>
         <v>0.32965001381244818</v>
       </c>
       <c r="AF20" s="20">
-        <f t="shared" si="36"/>
+        <f t="shared" si="45"/>
         <v>0.27042581934600368</v>
       </c>
       <c r="AG20" s="20">
-        <f t="shared" si="36"/>
+        <f t="shared" si="45"/>
         <v>0.30275436060156585</v>
       </c>
       <c r="AH20" s="20">
-        <f t="shared" si="36"/>
+        <f t="shared" si="45"/>
         <v>0.29572716743878225</v>
       </c>
-      <c r="AI20" s="21">
-        <f t="shared" si="36"/>
+      <c r="AI20" s="20">
+        <f t="shared" si="45"/>
         <v>0.30248423220491699</v>
       </c>
-      <c r="AJ20" s="20">
-        <f t="shared" si="36"/>
-        <v>0.3</v>
+      <c r="AJ20" s="21">
+        <f t="shared" si="45"/>
+        <v>0.2950000000000001</v>
       </c>
       <c r="AK20" s="20">
-        <f t="shared" si="36"/>
-        <v>0.30000000000000004</v>
+        <f t="shared" si="45"/>
+        <v>0.29499999999999998</v>
       </c>
       <c r="AL20" s="20">
-        <f t="shared" si="36"/>
-        <v>0.3</v>
+        <f t="shared" si="45"/>
+        <v>0.29500000000000004</v>
       </c>
       <c r="AM20" s="20">
-        <f t="shared" si="36"/>
-        <v>0.3</v>
+        <f t="shared" si="45"/>
+        <v>0.29500000000000004</v>
       </c>
       <c r="AN20" s="20">
-        <f t="shared" si="36"/>
-        <v>0.3000000000000001</v>
+        <f t="shared" si="45"/>
+        <v>0.29500000000000004</v>
       </c>
       <c r="AO20" s="20">
-        <f t="shared" si="36"/>
-        <v>0.30000000000000004</v>
+        <f t="shared" si="45"/>
+        <v>0.2950000000000001</v>
       </c>
       <c r="AP20" s="20">
-        <f t="shared" si="36"/>
-        <v>0.3000000000000001</v>
+        <f t="shared" si="45"/>
+        <v>0.29499999999999998</v>
       </c>
       <c r="AQ20" s="20">
-        <f t="shared" si="36"/>
-        <v>0.30000000000000004</v>
+        <f t="shared" si="45"/>
+        <v>0.29500000000000004</v>
       </c>
       <c r="AR20" s="20">
-        <f t="shared" si="36"/>
-        <v>0.3000000000000001</v>
+        <f t="shared" si="45"/>
+        <v>0.2950000000000001</v>
       </c>
       <c r="AS20" s="20">
-        <f t="shared" si="36"/>
-        <v>0.3000000000000001</v>
+        <f t="shared" si="45"/>
+        <v>0.29500000000000004</v>
       </c>
       <c r="AU20" s="2" t="s">
         <v>2</v>
@@ -5210,159 +5291,175 @@
         <v>39</v>
       </c>
       <c r="D21" s="20">
-        <f t="shared" ref="D21:S21" si="37">D10/D4</f>
+        <f t="shared" ref="D21:S21" si="46">D10/D4</f>
         <v>0.13764743385400063</v>
       </c>
       <c r="E21" s="20">
-        <f t="shared" si="37"/>
+        <f t="shared" si="46"/>
         <v>0.13069908814589665</v>
       </c>
       <c r="F21" s="20">
-        <f t="shared" si="37"/>
+        <f t="shared" si="46"/>
         <v>4.5551368179583808E-2</v>
       </c>
       <c r="G21" s="20">
-        <f t="shared" si="37"/>
+        <f t="shared" si="46"/>
         <v>-0.16777745580991016</v>
       </c>
       <c r="H21" s="20">
-        <f t="shared" si="37"/>
+        <f t="shared" si="46"/>
         <v>0.1377060639599231</v>
       </c>
       <c r="I21" s="20">
-        <f t="shared" si="37"/>
+        <f t="shared" si="46"/>
         <v>0.12376295947219604</v>
       </c>
       <c r="J21" s="20">
-        <f t="shared" si="37"/>
+        <f t="shared" si="46"/>
         <v>3.7861491628614914E-2</v>
       </c>
       <c r="K21" s="20">
-        <f t="shared" si="37"/>
+        <f t="shared" si="46"/>
         <v>-0.11423590935502614</v>
       </c>
       <c r="L21" s="20">
-        <f t="shared" si="37"/>
+        <f t="shared" si="46"/>
         <v>0.13112303824988111</v>
       </c>
       <c r="M21" s="20">
-        <f t="shared" si="37"/>
+        <f t="shared" si="46"/>
         <v>0.12300712896953986</v>
       </c>
       <c r="N21" s="20">
-        <f t="shared" si="37"/>
+        <f t="shared" si="46"/>
         <v>5.4420371701406718E-3</v>
       </c>
       <c r="O21" s="20">
-        <f t="shared" si="37"/>
+        <f t="shared" si="46"/>
         <v>-0.15181947069943288</v>
       </c>
       <c r="P21" s="20">
-        <f t="shared" si="37"/>
+        <f t="shared" si="46"/>
         <v>0.10412132752992383</v>
       </c>
       <c r="Q21" s="20">
-        <f t="shared" si="37"/>
+        <f t="shared" si="46"/>
         <v>0.13497414413824704</v>
       </c>
-      <c r="R21" s="51">
-        <f t="shared" si="37"/>
+      <c r="R21" s="20">
+        <f t="shared" si="46"/>
         <v>1.5428074750108649E-2</v>
       </c>
-      <c r="S21" s="21">
-        <f t="shared" si="37"/>
+      <c r="S21" s="20">
+        <f t="shared" si="46"/>
         <v>-0.11253196930946291</v>
       </c>
+      <c r="T21" s="20">
+        <f t="shared" ref="T21:W21" si="47">T10/T4</f>
+        <v>0.12247529007305544</v>
+      </c>
+      <c r="U21" s="20" t="e">
+        <f t="shared" si="47"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V21" s="20" t="e">
+        <f t="shared" si="47"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W21" s="20" t="e">
+        <f t="shared" si="47"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="Y21" s="20">
-        <f t="shared" ref="Y21:AS21" si="38">Y10/Y4</f>
+        <f t="shared" ref="Y21:AS21" si="48">Y10/Y4</f>
         <v>7.8158695051147364E-2</v>
       </c>
       <c r="Z21" s="20">
-        <f t="shared" si="38"/>
+        <f t="shared" si="48"/>
         <v>8.9433605691734752E-2</v>
       </c>
       <c r="AA21" s="20">
-        <f t="shared" si="38"/>
+        <f t="shared" si="48"/>
         <v>9.6207544296085704E-2</v>
       </c>
       <c r="AB21" s="20">
-        <f t="shared" si="38"/>
+        <f t="shared" si="48"/>
         <v>5.0383351588170866E-2</v>
       </c>
       <c r="AC21" s="20">
-        <f t="shared" si="38"/>
+        <f t="shared" si="48"/>
         <v>8.7281500579511312E-2</v>
       </c>
       <c r="AD21" s="20">
-        <f t="shared" si="38"/>
+        <f t="shared" si="48"/>
         <v>8.7475860095844363E-2</v>
       </c>
       <c r="AE21" s="20">
-        <f t="shared" si="38"/>
+        <f t="shared" si="48"/>
         <v>0.12210204211734206</v>
       </c>
       <c r="AF21" s="20">
-        <f t="shared" si="38"/>
+        <f t="shared" si="48"/>
         <v>5.6313266835686659E-2</v>
       </c>
       <c r="AG21" s="20">
-        <f t="shared" si="38"/>
+        <f t="shared" si="48"/>
         <v>7.2848801186609344E-2</v>
       </c>
       <c r="AH21" s="20">
-        <f t="shared" si="38"/>
+        <f t="shared" si="48"/>
         <v>5.3710291197882197E-2</v>
       </c>
-      <c r="AI21" s="21">
-        <f t="shared" si="38"/>
+      <c r="AI21" s="20">
+        <f t="shared" si="48"/>
         <v>6.2191616252627965E-2</v>
       </c>
-      <c r="AJ21" s="20">
-        <f t="shared" si="38"/>
-        <v>6.4930707512764432E-2</v>
+      <c r="AJ21" s="21">
+        <f t="shared" si="48"/>
+        <v>5.9930707512764518E-2</v>
       </c>
       <c r="AK21" s="20">
-        <f t="shared" si="38"/>
-        <v>6.493070751276446E-2</v>
+        <f t="shared" si="48"/>
+        <v>5.9930707512764393E-2</v>
       </c>
       <c r="AL21" s="20">
-        <f t="shared" si="38"/>
-        <v>6.4930707512764391E-2</v>
+        <f t="shared" si="48"/>
+        <v>5.9930707512764428E-2</v>
       </c>
       <c r="AM21" s="20">
-        <f t="shared" si="38"/>
-        <v>6.7169462679309511E-2</v>
+        <f t="shared" si="48"/>
+        <v>6.2169462679309562E-2</v>
       </c>
       <c r="AN21" s="20">
-        <f t="shared" si="38"/>
-        <v>6.9386896368078113E-2</v>
+        <f t="shared" si="48"/>
+        <v>6.4386896368078039E-2</v>
       </c>
       <c r="AO21" s="20">
-        <f t="shared" si="38"/>
-        <v>7.1583211640763048E-2</v>
+        <f t="shared" si="48"/>
+        <v>6.6583211640763085E-2</v>
       </c>
       <c r="AP21" s="20">
-        <f t="shared" si="38"/>
-        <v>7.3758609625136765E-2</v>
+        <f t="shared" si="48"/>
+        <v>6.8758609625136663E-2</v>
       </c>
       <c r="AQ21" s="20">
-        <f t="shared" si="38"/>
-        <v>7.591328953346875E-2</v>
+        <f t="shared" si="48"/>
+        <v>7.0913289533468732E-2</v>
       </c>
       <c r="AR21" s="20">
-        <f t="shared" si="38"/>
-        <v>7.8047448680769099E-2</v>
+        <f t="shared" si="48"/>
+        <v>7.3047448680769095E-2</v>
       </c>
       <c r="AS21" s="20">
-        <f t="shared" si="38"/>
-        <v>8.0161282502857006E-2</v>
+        <f t="shared" si="48"/>
+        <v>7.5161282502856946E-2</v>
       </c>
       <c r="AU21" s="2" t="s">
         <v>121</v>
       </c>
       <c r="AV21" s="9">
         <f>AV19/AV20</f>
-        <v>76.947408658985822</v>
+        <v>71.838140960659828</v>
       </c>
     </row>
     <row r="22" spans="3:48" x14ac:dyDescent="0.25">
@@ -5417,7 +5514,7 @@
       </c>
       <c r="AV22" s="18">
         <f>(AV21-B4)/B4</f>
-        <v>0.83864775768185951</v>
+        <v>0.57160667163989998</v>
       </c>
     </row>
     <row r="23" spans="3:48" x14ac:dyDescent="0.25">
@@ -5506,13 +5603,15 @@
       <c r="Q25" s="14">
         <v>6981</v>
       </c>
-      <c r="R25" s="48">
+      <c r="R25" s="14">
         <v>6879</v>
       </c>
-      <c r="S25" s="15">
+      <c r="S25" s="14">
         <v>6668</v>
       </c>
-      <c r="T25" s="12"/>
+      <c r="T25" s="14">
+        <v>6607</v>
+      </c>
       <c r="U25" s="1"/>
       <c r="V25" s="1"/>
       <c r="W25" s="1"/>
@@ -5572,13 +5671,15 @@
       <c r="Q26" s="14">
         <v>1710</v>
       </c>
-      <c r="R26" s="48">
+      <c r="R26" s="14">
         <v>1600</v>
       </c>
-      <c r="S26" s="15">
+      <c r="S26" s="14">
         <v>1641</v>
       </c>
-      <c r="T26" s="14"/>
+      <c r="T26" s="14">
+        <v>1653</v>
+      </c>
       <c r="AH26" s="14"/>
     </row>
     <row r="27" spans="3:48" x14ac:dyDescent="0.25">
@@ -5627,20 +5728,22 @@
       <c r="Q27" s="14">
         <v>9633</v>
       </c>
-      <c r="R27" s="48">
+      <c r="R27" s="14">
         <v>9569</v>
       </c>
-      <c r="S27" s="15">
+      <c r="S27" s="14">
         <v>9380</v>
       </c>
-      <c r="T27" s="14"/>
+      <c r="T27" s="14">
+        <v>9620</v>
+      </c>
       <c r="U27" s="20"/>
       <c r="V27" s="20"/>
       <c r="W27" s="20"/>
       <c r="X27" s="20"/>
       <c r="AH27" s="14"/>
-      <c r="AI27" s="21"/>
-      <c r="AJ27" s="20"/>
+      <c r="AI27" s="20"/>
+      <c r="AJ27" s="21"/>
       <c r="AK27" s="20"/>
       <c r="AL27" s="20"/>
       <c r="AM27" s="20"/>
@@ -5697,13 +5800,15 @@
       <c r="Q28" s="14">
         <v>8510</v>
       </c>
-      <c r="R28" s="48">
+      <c r="R28" s="14">
         <v>8375</v>
       </c>
-      <c r="S28" s="15">
+      <c r="S28" s="14">
         <v>8265</v>
       </c>
-      <c r="T28" s="14"/>
+      <c r="T28" s="14">
+        <v>8310</v>
+      </c>
       <c r="AH28" s="14"/>
     </row>
     <row r="29" spans="3:48" x14ac:dyDescent="0.25">
@@ -5752,13 +5857,15 @@
       <c r="Q29" s="14">
         <v>32</v>
       </c>
-      <c r="R29" s="48">
+      <c r="R29" s="14">
         <v>32</v>
       </c>
-      <c r="S29" s="15">
+      <c r="S29" s="14">
         <v>2</v>
       </c>
-      <c r="T29" s="14"/>
+      <c r="T29" s="14">
+        <v>2</v>
+      </c>
       <c r="AH29" s="14"/>
     </row>
     <row r="30" spans="3:48" x14ac:dyDescent="0.25">
@@ -5807,13 +5914,15 @@
       <c r="Q30" s="14">
         <v>0</v>
       </c>
-      <c r="R30" s="48">
+      <c r="R30" s="14">
         <v>0</v>
       </c>
-      <c r="S30" s="15">
+      <c r="S30" s="14">
         <v>13</v>
       </c>
-      <c r="T30" s="14"/>
+      <c r="T30" s="14">
+        <v>44</v>
+      </c>
       <c r="AH30" s="14"/>
     </row>
     <row r="31" spans="3:48" x14ac:dyDescent="0.25">
@@ -5862,13 +5971,15 @@
       <c r="Q31" s="14">
         <v>891</v>
       </c>
-      <c r="R31" s="48">
+      <c r="R31" s="14">
         <v>879</v>
       </c>
-      <c r="S31" s="15">
+      <c r="S31" s="14">
         <v>1072</v>
       </c>
-      <c r="T31" s="14"/>
+      <c r="T31" s="14">
+        <v>1093</v>
+      </c>
       <c r="AH31" s="14"/>
     </row>
     <row r="32" spans="3:48" x14ac:dyDescent="0.25">
@@ -5917,13 +6028,15 @@
       <c r="Q32" s="14">
         <v>1856</v>
       </c>
-      <c r="R32" s="48">
+      <c r="R32" s="14">
         <v>1836</v>
       </c>
-      <c r="S32" s="15">
+      <c r="S32" s="14">
         <v>1828</v>
       </c>
-      <c r="T32" s="14"/>
+      <c r="T32" s="14">
+        <v>1511</v>
+      </c>
       <c r="AH32" s="14"/>
     </row>
     <row r="33" spans="3:34" x14ac:dyDescent="0.25">
@@ -5972,13 +6085,15 @@
       <c r="Q33" s="14">
         <v>11954</v>
       </c>
-      <c r="R33" s="48">
+      <c r="R33" s="14">
         <v>12248</v>
       </c>
-      <c r="S33" s="15">
+      <c r="S33" s="14">
         <v>13847</v>
       </c>
-      <c r="T33" s="14"/>
+      <c r="T33" s="14">
+        <v>13952</v>
+      </c>
       <c r="AH33" s="14"/>
     </row>
     <row r="34" spans="3:34" x14ac:dyDescent="0.25">
@@ -6027,13 +6142,12 @@
       <c r="Q34" s="14">
         <v>0</v>
       </c>
-      <c r="R34" s="48">
+      <c r="R34" s="14">
         <v>0</v>
       </c>
-      <c r="S34" s="15">
+      <c r="S34" s="14">
         <v>0</v>
       </c>
-      <c r="T34" s="14"/>
       <c r="AH34" s="14"/>
     </row>
     <row r="35" spans="3:34" x14ac:dyDescent="0.25">
@@ -6082,13 +6196,15 @@
       <c r="Q35" s="14">
         <v>10683</v>
       </c>
-      <c r="R35" s="48">
+      <c r="R35" s="14">
         <v>5730</v>
       </c>
-      <c r="S35" s="15">
+      <c r="S35" s="14">
         <v>4990</v>
       </c>
-      <c r="T35" s="14"/>
+      <c r="T35" s="14">
+        <v>11219</v>
+      </c>
       <c r="AH35" s="14"/>
     </row>
     <row r="36" spans="3:34" x14ac:dyDescent="0.25">
@@ -6137,14 +6253,15 @@
       <c r="Q36" s="14">
         <v>438</v>
       </c>
-      <c r="R36" s="48">
+      <c r="R36" s="14">
         <v>321</v>
       </c>
-      <c r="S36" s="15">
+      <c r="S36" s="14">
         <v>577</v>
       </c>
-      <c r="T36" s="14"/>
-      <c r="AH36" s="45"/>
+      <c r="T36" s="14">
+        <v>308</v>
+      </c>
     </row>
     <row r="37" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C37" s="2" t="s">
@@ -6192,13 +6309,15 @@
       <c r="Q37" s="14">
         <v>477</v>
       </c>
-      <c r="R37" s="48">
+      <c r="R37" s="14">
         <v>427</v>
       </c>
-      <c r="S37" s="15">
+      <c r="S37" s="14">
         <v>462</v>
       </c>
-      <c r="T37" s="14"/>
+      <c r="T37" s="14">
+        <v>417</v>
+      </c>
       <c r="AH37" s="14"/>
     </row>
     <row r="38" spans="3:34" x14ac:dyDescent="0.25">
@@ -6247,13 +6366,15 @@
       <c r="Q38" s="14">
         <v>1775</v>
       </c>
-      <c r="R38" s="48">
+      <c r="R38" s="14">
         <v>1667</v>
       </c>
-      <c r="S38" s="15">
+      <c r="S38" s="14">
         <v>1641</v>
       </c>
-      <c r="T38" s="14"/>
+      <c r="T38" s="14">
+        <v>1788</v>
+      </c>
     </row>
     <row r="39" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C39" s="2" t="s">
@@ -6301,56 +6422,58 @@
       <c r="Q39" s="14">
         <v>3475</v>
       </c>
-      <c r="R39" s="48">
+      <c r="R39" s="14">
         <v>3895</v>
       </c>
-      <c r="S39" s="15">
+      <c r="S39" s="14">
         <v>1707</v>
       </c>
-      <c r="T39" s="14"/>
+      <c r="T39" s="14">
+        <v>1708</v>
+      </c>
     </row>
     <row r="40" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C40" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D40" s="12">
-        <f t="shared" ref="D40:P40" si="39">SUM(D25:D39)</f>
+        <f t="shared" ref="D40:P40" si="49">SUM(D25:D39)</f>
         <v>57189</v>
       </c>
       <c r="E40" s="12">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>59388</v>
       </c>
       <c r="F40" s="12">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>60425</v>
       </c>
       <c r="G40" s="12">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>61636</v>
       </c>
       <c r="H40" s="12">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>65567</v>
       </c>
       <c r="I40" s="12">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>66270</v>
       </c>
       <c r="J40" s="12">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>59590</v>
       </c>
       <c r="K40" s="12">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>57610</v>
       </c>
       <c r="L40" s="12">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>64344</v>
       </c>
       <c r="M40" s="12">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>60468.130000000005</v>
       </c>
       <c r="N40" s="12">
@@ -6358,28 +6481,28 @@
         <v>55234</v>
       </c>
       <c r="O40" s="12">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>56805</v>
       </c>
       <c r="P40" s="12">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>59448</v>
       </c>
       <c r="Q40" s="12">
         <f>SUM(Q25:Q39)</f>
         <v>58415</v>
       </c>
-      <c r="R40" s="47">
-        <f t="shared" ref="R40:T40" si="40">SUM(R25:R39)</f>
+      <c r="R40" s="12">
+        <f t="shared" ref="R40:S40" si="50">SUM(R25:R39)</f>
         <v>53458</v>
       </c>
-      <c r="S40" s="13">
-        <f t="shared" si="40"/>
+      <c r="S40" s="12">
+        <f t="shared" si="50"/>
         <v>52093</v>
       </c>
       <c r="T40" s="12">
-        <f t="shared" si="40"/>
-        <v>0</v>
+        <f>SUM(T25:T39)</f>
+        <v>58232</v>
       </c>
       <c r="U40" s="12"/>
       <c r="V40" s="12"/>
@@ -6432,13 +6555,15 @@
       <c r="Q41" s="14">
         <v>24641</v>
       </c>
-      <c r="R41" s="48">
+      <c r="R41" s="14">
         <v>24640</v>
       </c>
-      <c r="S41" s="15">
+      <c r="S41" s="14">
         <v>23637</v>
       </c>
-      <c r="T41" s="14"/>
+      <c r="T41" s="14">
+        <v>25157</v>
+      </c>
     </row>
     <row r="42" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C42" s="2" t="s">
@@ -6486,13 +6611,15 @@
       <c r="Q42" s="14">
         <v>4</v>
       </c>
-      <c r="R42" s="48">
+      <c r="R42" s="14">
         <v>4</v>
       </c>
-      <c r="S42" s="15">
+      <c r="S42" s="14">
         <v>3</v>
       </c>
-      <c r="T42" s="16"/>
+      <c r="T42" s="16">
+        <v>4</v>
+      </c>
       <c r="U42" s="11"/>
       <c r="V42" s="11"/>
       <c r="W42" s="11"/>
@@ -6502,72 +6629,72 @@
         <v>86</v>
       </c>
       <c r="D43" s="16">
-        <f t="shared" ref="D43:P43" si="41">SUM(D41:D42)</f>
+        <f t="shared" ref="D43:P43" si="51">SUM(D41:D42)</f>
         <v>23671</v>
       </c>
       <c r="E43" s="16">
-        <f t="shared" si="41"/>
+        <f t="shared" si="51"/>
         <v>25034</v>
       </c>
       <c r="F43" s="16">
-        <f t="shared" si="41"/>
+        <f t="shared" si="51"/>
         <v>26472</v>
       </c>
       <c r="G43" s="16">
-        <f t="shared" si="41"/>
+        <f t="shared" si="51"/>
         <v>24012</v>
       </c>
       <c r="H43" s="16">
-        <f t="shared" si="41"/>
+        <f t="shared" si="51"/>
         <v>25817</v>
       </c>
       <c r="I43" s="16">
-        <f t="shared" si="41"/>
+        <f t="shared" si="51"/>
         <v>26279</v>
       </c>
       <c r="J43" s="16">
-        <f t="shared" si="41"/>
+        <f t="shared" si="51"/>
         <v>26129</v>
       </c>
       <c r="K43" s="16">
-        <f t="shared" si="41"/>
+        <f t="shared" si="51"/>
         <v>23772</v>
       </c>
       <c r="L43" s="16">
-        <f t="shared" si="41"/>
+        <f t="shared" si="51"/>
         <v>25964</v>
       </c>
       <c r="M43" s="16">
-        <f t="shared" si="41"/>
+        <f t="shared" si="51"/>
         <v>25515</v>
       </c>
       <c r="N43" s="16">
-        <f t="shared" si="41"/>
+        <f t="shared" si="51"/>
         <v>24703</v>
       </c>
       <c r="O43" s="16">
-        <f t="shared" si="41"/>
+        <f t="shared" si="51"/>
         <v>24622</v>
       </c>
       <c r="P43" s="16">
-        <f t="shared" si="41"/>
+        <f t="shared" si="51"/>
         <v>24167</v>
       </c>
       <c r="Q43" s="16">
         <f>SUM(Q41:Q42)</f>
         <v>24645</v>
       </c>
-      <c r="R43" s="52">
-        <f t="shared" ref="R43:T43" si="42">SUM(R41:R42)</f>
+      <c r="R43" s="16">
+        <f t="shared" ref="R43:T43" si="52">SUM(R41:R42)</f>
         <v>24644</v>
       </c>
-      <c r="S43" s="37">
-        <f t="shared" si="42"/>
+      <c r="S43" s="16">
+        <f t="shared" si="52"/>
         <v>23640</v>
       </c>
       <c r="T43" s="16">
-        <f t="shared" si="42"/>
-        <v>0</v>
+        <f t="shared" si="52"/>
+        <v>25161</v>
       </c>
       <c r="U43" s="16"/>
       <c r="V43" s="16"/>
@@ -6620,13 +6747,15 @@
       <c r="Q44" s="14">
         <v>9816</v>
       </c>
-      <c r="R44" s="48">
+      <c r="R44" s="14">
         <v>9802</v>
       </c>
-      <c r="S44" s="15">
+      <c r="S44" s="14">
         <v>9200</v>
       </c>
-      <c r="T44" s="14"/>
+      <c r="T44" s="14">
+        <v>8485</v>
+      </c>
     </row>
     <row r="45" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C45" s="2" t="s">
@@ -6674,13 +6803,15 @@
       <c r="Q45" s="14">
         <v>1108</v>
       </c>
-      <c r="R45" s="48">
+      <c r="R45" s="14">
         <v>1028</v>
       </c>
-      <c r="S45" s="15">
+      <c r="S45" s="14">
         <v>1199</v>
       </c>
-      <c r="T45" s="14"/>
+      <c r="T45" s="14">
+        <v>1195</v>
+      </c>
     </row>
     <row r="46" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C46" s="2" t="s">
@@ -6728,13 +6859,15 @@
       <c r="Q46" s="14">
         <v>49</v>
       </c>
-      <c r="R46" s="48">
+      <c r="R46" s="14">
         <v>41</v>
       </c>
-      <c r="S46" s="15">
+      <c r="S46" s="14">
         <v>18</v>
       </c>
-      <c r="T46" s="14"/>
+      <c r="T46" s="14">
+        <v>0</v>
+      </c>
     </row>
     <row r="47" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C47" s="2" t="s">
@@ -6782,13 +6915,15 @@
       <c r="Q47" s="14">
         <v>2205</v>
       </c>
-      <c r="R47" s="48">
+      <c r="R47" s="14">
         <v>2167</v>
       </c>
-      <c r="S47" s="15">
+      <c r="S47" s="14">
         <v>2291</v>
       </c>
-      <c r="T47" s="14"/>
+      <c r="T47" s="14">
+        <v>1943</v>
+      </c>
     </row>
     <row r="48" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C48" s="2" t="s">
@@ -6836,13 +6971,15 @@
       <c r="Q48" s="14">
         <v>2040</v>
       </c>
-      <c r="R48" s="48">
+      <c r="R48" s="14">
         <v>1931</v>
       </c>
-      <c r="S48" s="15">
+      <c r="S48" s="14">
         <v>1905</v>
       </c>
-      <c r="T48" s="14"/>
+      <c r="T48" s="14">
+        <v>2042</v>
+      </c>
     </row>
     <row r="49" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C49" s="2" t="s">
@@ -6890,13 +7027,15 @@
       <c r="Q49" s="14">
         <v>641</v>
       </c>
-      <c r="R49" s="48">
+      <c r="R49" s="14">
         <v>600</v>
       </c>
-      <c r="S49" s="15">
+      <c r="S49" s="14">
         <v>556</v>
       </c>
-      <c r="T49" s="14"/>
+      <c r="T49" s="14">
+        <v>597</v>
+      </c>
     </row>
     <row r="50" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C50" s="2" t="s">
@@ -6944,13 +7083,15 @@
       <c r="Q50" s="14">
         <v>6786</v>
       </c>
-      <c r="R50" s="48">
+      <c r="R50" s="14">
         <v>5253</v>
       </c>
-      <c r="S50" s="15">
+      <c r="S50" s="14">
         <v>5786</v>
       </c>
-      <c r="T50" s="14"/>
+      <c r="T50" s="14">
+        <v>6827</v>
+      </c>
     </row>
     <row r="51" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C51" s="2" t="s">
@@ -6998,13 +7139,15 @@
       <c r="Q51" s="14">
         <v>786</v>
       </c>
-      <c r="R51" s="48">
+      <c r="R51" s="14">
         <v>695</v>
       </c>
-      <c r="S51" s="15">
+      <c r="S51" s="14">
         <v>381</v>
       </c>
-      <c r="T51" s="14"/>
+      <c r="T51" s="14">
+        <v>513</v>
+      </c>
     </row>
     <row r="52" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C52" s="2" t="s">
@@ -7052,13 +7195,15 @@
       <c r="Q52" s="14">
         <v>5330</v>
       </c>
-      <c r="R52" s="48">
+      <c r="R52" s="14">
         <v>4350</v>
       </c>
-      <c r="S52" s="15">
+      <c r="S52" s="14">
         <v>3814</v>
       </c>
-      <c r="T52" s="14"/>
+      <c r="T52" s="14">
+        <v>5675</v>
+      </c>
       <c r="AC52" s="1"/>
       <c r="AD52" s="1"/>
       <c r="AE52" s="1"/>
@@ -7112,13 +7257,15 @@
       <c r="Q53" s="14">
         <v>288</v>
       </c>
-      <c r="R53" s="48">
+      <c r="R53" s="14">
         <v>288</v>
       </c>
-      <c r="S53" s="15">
+      <c r="S53" s="14">
         <v>1716</v>
       </c>
-      <c r="T53" s="14"/>
+      <c r="T53" s="14">
+        <v>3592</v>
+      </c>
     </row>
     <row r="54" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C54" s="2" t="s">
@@ -7166,13 +7313,15 @@
       <c r="Q54" s="14">
         <v>2492</v>
       </c>
-      <c r="R54" s="48">
+      <c r="R54" s="14">
         <v>697</v>
       </c>
-      <c r="S54" s="15">
+      <c r="S54" s="14">
         <v>616</v>
       </c>
-      <c r="T54" s="14"/>
+      <c r="T54" s="14">
+        <v>621</v>
+      </c>
     </row>
     <row r="55" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C55" s="2" t="s">
@@ -7220,13 +7369,15 @@
       <c r="Q55" s="14">
         <v>618</v>
       </c>
-      <c r="R55" s="48">
+      <c r="R55" s="14">
         <v>586</v>
       </c>
-      <c r="S55" s="15">
+      <c r="S55" s="14">
         <v>249</v>
       </c>
-      <c r="T55" s="14"/>
+      <c r="T55" s="14">
+        <v>678</v>
+      </c>
     </row>
     <row r="56" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C56" s="2" t="s">
@@ -7274,13 +7425,15 @@
       <c r="Q56" s="14">
         <v>357</v>
       </c>
-      <c r="R56" s="48">
+      <c r="R56" s="14">
         <v>285</v>
       </c>
-      <c r="S56" s="15">
+      <c r="S56" s="14">
         <v>823</v>
       </c>
-      <c r="T56" s="14"/>
+      <c r="T56" s="14">
+        <v>905</v>
+      </c>
       <c r="AC56" s="1"/>
       <c r="AD56" s="1"/>
       <c r="AE56" s="1"/>
@@ -7334,13 +7487,15 @@
       <c r="Q57" s="14">
         <v>1253</v>
       </c>
-      <c r="R57" s="48">
+      <c r="R57" s="14">
         <v>1118</v>
       </c>
-      <c r="S57" s="15">
+      <c r="S57" s="14">
         <v>0</v>
       </c>
-      <c r="T57" s="14"/>
+      <c r="T57" s="14">
+        <v>0</v>
+      </c>
     </row>
     <row r="58" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C58" s="2" t="s">
@@ -7388,85 +7543,87 @@
       <c r="Q58" s="14">
         <v>0</v>
       </c>
-      <c r="R58" s="48">
+      <c r="R58" s="14">
         <v>0</v>
       </c>
-      <c r="S58" s="15">
+      <c r="S58" s="14">
         <v>0</v>
       </c>
-      <c r="T58" s="14"/>
+      <c r="T58" s="14">
+        <v>0</v>
+      </c>
     </row>
     <row r="59" spans="3:34" x14ac:dyDescent="0.25">
       <c r="C59" s="11" t="s">
         <v>96</v>
       </c>
       <c r="D59" s="16">
-        <f t="shared" ref="D59:P59" si="43">SUM(D44:D58)</f>
+        <f t="shared" ref="D59:P59" si="53">SUM(D44:D58)</f>
         <v>33518</v>
       </c>
       <c r="E59" s="16">
-        <f t="shared" si="43"/>
+        <f t="shared" si="53"/>
         <v>34352</v>
       </c>
       <c r="F59" s="16">
-        <f t="shared" si="43"/>
+        <f t="shared" si="53"/>
         <v>33952</v>
       </c>
       <c r="G59" s="16">
-        <f t="shared" si="43"/>
+        <f t="shared" si="53"/>
         <v>37624</v>
       </c>
       <c r="H59" s="16">
-        <f t="shared" si="43"/>
+        <f t="shared" si="53"/>
         <v>39751</v>
       </c>
       <c r="I59" s="16">
-        <f t="shared" si="43"/>
+        <f t="shared" si="53"/>
         <v>39991</v>
       </c>
       <c r="J59" s="16">
-        <f t="shared" si="43"/>
+        <f t="shared" si="53"/>
         <v>33456</v>
       </c>
       <c r="K59" s="16">
-        <f t="shared" si="43"/>
+        <f t="shared" si="53"/>
         <v>33839</v>
       </c>
       <c r="L59" s="16">
-        <f t="shared" si="43"/>
+        <f t="shared" si="53"/>
         <v>38379</v>
       </c>
       <c r="M59" s="16">
-        <f t="shared" si="43"/>
+        <f t="shared" si="53"/>
         <v>34966</v>
       </c>
       <c r="N59" s="16">
-        <f t="shared" si="43"/>
+        <f t="shared" si="53"/>
         <v>30531</v>
       </c>
       <c r="O59" s="16">
-        <f t="shared" si="43"/>
+        <f t="shared" si="53"/>
         <v>32181</v>
       </c>
       <c r="P59" s="16">
-        <f t="shared" si="43"/>
+        <f t="shared" si="53"/>
         <v>35282</v>
       </c>
       <c r="Q59" s="16">
         <f>SUM(Q44:Q58)</f>
         <v>33769</v>
       </c>
-      <c r="R59" s="52">
-        <f t="shared" ref="R59:T59" si="44">SUM(R44:R58)</f>
+      <c r="R59" s="16">
+        <f t="shared" ref="R59:T59" si="54">SUM(R44:R58)</f>
         <v>28841</v>
       </c>
-      <c r="S59" s="37">
-        <f t="shared" si="44"/>
+      <c r="S59" s="16">
+        <f t="shared" si="54"/>
         <v>28554</v>
       </c>
       <c r="T59" s="16">
-        <f t="shared" si="44"/>
-        <v>0</v>
+        <f t="shared" si="54"/>
+        <v>33073</v>
       </c>
       <c r="U59" s="16"/>
       <c r="V59" s="16"/>
@@ -7478,72 +7635,72 @@
         <v>97</v>
       </c>
       <c r="D60" s="12">
-        <f t="shared" ref="D60:P60" si="45">D43+D59</f>
+        <f t="shared" ref="D60:P60" si="55">D43+D59</f>
         <v>57189</v>
       </c>
       <c r="E60" s="12">
-        <f t="shared" si="45"/>
+        <f t="shared" si="55"/>
         <v>59386</v>
       </c>
       <c r="F60" s="12">
-        <f t="shared" si="45"/>
+        <f t="shared" si="55"/>
         <v>60424</v>
       </c>
       <c r="G60" s="12">
-        <f t="shared" si="45"/>
+        <f t="shared" si="55"/>
         <v>61636</v>
       </c>
       <c r="H60" s="12">
-        <f t="shared" si="45"/>
+        <f t="shared" si="55"/>
         <v>65568</v>
       </c>
       <c r="I60" s="12">
-        <f t="shared" si="45"/>
+        <f t="shared" si="55"/>
         <v>66270</v>
       </c>
       <c r="J60" s="12">
-        <f t="shared" si="45"/>
+        <f t="shared" si="55"/>
         <v>59585</v>
       </c>
       <c r="K60" s="12">
-        <f t="shared" si="45"/>
+        <f t="shared" si="55"/>
         <v>57611</v>
       </c>
       <c r="L60" s="12">
-        <f t="shared" si="45"/>
+        <f t="shared" si="55"/>
         <v>64343</v>
       </c>
       <c r="M60" s="12">
-        <f t="shared" si="45"/>
+        <f t="shared" si="55"/>
         <v>60481</v>
       </c>
       <c r="N60" s="12">
-        <f t="shared" si="45"/>
+        <f t="shared" si="55"/>
         <v>55234</v>
       </c>
       <c r="O60" s="12">
-        <f t="shared" si="45"/>
+        <f t="shared" si="55"/>
         <v>56803</v>
       </c>
       <c r="P60" s="12">
-        <f t="shared" si="45"/>
+        <f t="shared" si="55"/>
         <v>59449</v>
       </c>
       <c r="Q60" s="12">
         <f>Q43+Q59</f>
         <v>58414</v>
       </c>
-      <c r="R60" s="47">
-        <f t="shared" ref="R60:T60" si="46">R43+R59</f>
+      <c r="R60" s="12">
+        <f t="shared" ref="R60:T60" si="56">R43+R59</f>
         <v>53485</v>
       </c>
-      <c r="S60" s="13">
-        <f t="shared" si="46"/>
+      <c r="S60" s="12">
+        <f t="shared" si="56"/>
         <v>52194</v>
       </c>
       <c r="T60" s="12">
-        <f t="shared" si="46"/>
-        <v>0</v>
+        <f t="shared" si="56"/>
+        <v>58234</v>
       </c>
       <c r="U60" s="12"/>
       <c r="V60" s="12"/>
@@ -7592,8 +7749,8 @@
       <c r="M62" s="14"/>
       <c r="N62" s="14"/>
       <c r="Q62" s="1"/>
-      <c r="R62" s="53"/>
-      <c r="S62" s="36"/>
+      <c r="R62" s="1"/>
+      <c r="S62" s="1"/>
       <c r="T62" s="1"/>
       <c r="U62" s="1"/>
       <c r="V62" s="1"/>
@@ -7604,39 +7761,39 @@
         <v>2827</v>
       </c>
       <c r="Z62" s="14">
-        <f t="shared" ref="Z62:AH62" si="47">Z10</f>
+        <f t="shared" ref="Z62:AH62" si="57">Z10</f>
         <v>3218</v>
       </c>
       <c r="AA62" s="14">
-        <f t="shared" si="47"/>
+        <f t="shared" si="57"/>
         <v>3790</v>
       </c>
       <c r="AB62" s="14">
-        <f t="shared" si="47"/>
+        <f t="shared" si="57"/>
         <v>2070</v>
       </c>
       <c r="AC62" s="14">
-        <f t="shared" si="47"/>
+        <f t="shared" si="57"/>
         <v>3690</v>
       </c>
       <c r="AD62" s="14">
-        <f t="shared" si="47"/>
+        <f t="shared" si="57"/>
         <v>3669</v>
       </c>
       <c r="AE62" s="14">
-        <f t="shared" si="47"/>
+        <f t="shared" si="57"/>
         <v>5746</v>
       </c>
       <c r="AF62" s="14">
-        <f t="shared" si="47"/>
+        <f t="shared" si="57"/>
         <v>3043</v>
       </c>
       <c r="AG62" s="14">
-        <f t="shared" si="47"/>
+        <f t="shared" si="57"/>
         <v>3880</v>
       </c>
       <c r="AH62" s="14">
-        <f t="shared" si="47"/>
+        <f t="shared" si="57"/>
         <v>2597</v>
       </c>
     </row>
@@ -7645,72 +7802,72 @@
         <v>98</v>
       </c>
       <c r="D63" s="14">
-        <f t="shared" ref="D63:T63" si="48">D10</f>
+        <f t="shared" ref="D63:T63" si="58">D10</f>
         <v>2159</v>
       </c>
       <c r="E63" s="14">
-        <f t="shared" si="48"/>
+        <f t="shared" si="58"/>
         <v>2064</v>
       </c>
       <c r="F63" s="14">
-        <f t="shared" si="48"/>
+        <f t="shared" si="58"/>
         <v>556</v>
       </c>
       <c r="G63" s="14">
-        <f t="shared" si="48"/>
+        <f t="shared" si="58"/>
         <v>-1737</v>
       </c>
       <c r="H63" s="14">
-        <f t="shared" si="48"/>
+        <f t="shared" si="58"/>
         <v>2364</v>
       </c>
       <c r="I63" s="14">
-        <f t="shared" si="48"/>
+        <f t="shared" si="58"/>
         <v>2101</v>
       </c>
       <c r="J63" s="14">
-        <f t="shared" si="48"/>
+        <f t="shared" si="58"/>
         <v>398</v>
       </c>
       <c r="K63" s="14">
-        <f t="shared" si="48"/>
+        <f t="shared" si="58"/>
         <v>-983</v>
       </c>
       <c r="L63" s="14">
-        <f t="shared" si="48"/>
+        <f t="shared" si="58"/>
         <v>1930</v>
       </c>
       <c r="M63" s="14">
-        <f t="shared" si="48"/>
+        <f t="shared" si="58"/>
         <v>1898</v>
       </c>
       <c r="N63" s="14">
-        <f t="shared" si="48"/>
+        <f t="shared" si="58"/>
         <v>53</v>
       </c>
       <c r="O63" s="14">
-        <f t="shared" si="48"/>
+        <f t="shared" si="58"/>
         <v>-1285</v>
       </c>
       <c r="P63" s="14">
-        <f t="shared" si="48"/>
+        <f t="shared" si="58"/>
         <v>1531</v>
       </c>
       <c r="Q63" s="14">
-        <f t="shared" si="48"/>
+        <f t="shared" si="58"/>
         <v>2062</v>
       </c>
-      <c r="R63" s="48">
-        <f t="shared" si="48"/>
+      <c r="R63" s="14">
+        <f t="shared" si="58"/>
         <v>142</v>
       </c>
-      <c r="S63" s="15">
-        <f t="shared" si="48"/>
+      <c r="S63" s="14">
+        <f t="shared" si="58"/>
         <v>-836</v>
       </c>
       <c r="T63" s="14">
-        <f t="shared" si="48"/>
-        <v>0</v>
+        <f t="shared" si="58"/>
+        <v>1710</v>
       </c>
       <c r="U63" s="14"/>
       <c r="V63" s="14"/>
@@ -7793,13 +7950,15 @@
       <c r="Q64" s="14">
         <v>2063</v>
       </c>
-      <c r="R64" s="48">
+      <c r="R64" s="14">
         <v>141</v>
       </c>
-      <c r="S64" s="15">
+      <c r="S64" s="14">
         <v>-837</v>
       </c>
-      <c r="T64" s="14"/>
+      <c r="T64" s="14">
+        <v>1710</v>
+      </c>
       <c r="X64" s="1"/>
       <c r="Y64" s="14">
         <f>1153+253</f>
@@ -7888,13 +8047,15 @@
       <c r="Q65" s="14">
         <v>905</v>
       </c>
-      <c r="R65" s="48">
+      <c r="R65" s="14">
         <v>711</v>
       </c>
-      <c r="S65" s="15">
+      <c r="S65" s="14">
         <v>595</v>
       </c>
-      <c r="T65" s="14"/>
+      <c r="T65" s="14">
+        <v>888</v>
+      </c>
       <c r="X65" s="1"/>
       <c r="Y65" s="14">
         <v>-27</v>
@@ -7973,13 +8134,15 @@
       <c r="Q66" s="14">
         <v>-153</v>
       </c>
-      <c r="R66" s="48">
+      <c r="R66" s="14">
         <v>-96</v>
       </c>
-      <c r="S66" s="15">
+      <c r="S66" s="14">
         <v>-181</v>
       </c>
-      <c r="T66" s="14"/>
+      <c r="T66" s="14">
+        <v>-56</v>
+      </c>
       <c r="X66" s="1"/>
       <c r="Y66" s="14">
         <v>-251</v>
@@ -8058,13 +8221,15 @@
       <c r="Q67" s="14">
         <v>-156</v>
       </c>
-      <c r="R67" s="48">
+      <c r="R67" s="14">
         <v>-141</v>
       </c>
-      <c r="S67" s="15">
+      <c r="S67" s="14">
         <v>-128</v>
       </c>
-      <c r="T67" s="14"/>
+      <c r="T67" s="14">
+        <v>-173</v>
+      </c>
       <c r="Y67" s="14">
         <v>-252</v>
       </c>
@@ -8142,13 +8307,15 @@
       <c r="Q68" s="14">
         <v>-133</v>
       </c>
-      <c r="R68" s="48">
+      <c r="R68" s="14">
         <v>-56</v>
       </c>
-      <c r="S68" s="15">
+      <c r="S68" s="14">
         <v>-60</v>
       </c>
-      <c r="T68" s="14"/>
+      <c r="T68" s="14">
+        <v>-82</v>
+      </c>
       <c r="Y68" s="14">
         <f>-89-287-175-32</f>
         <v>-583</v>
@@ -8250,53 +8417,55 @@
         <f>1085-171-744+130</f>
         <v>300</v>
       </c>
-      <c r="R69" s="48">
+      <c r="R69" s="14">
         <f>-383+4990-1542-824</f>
         <v>2241</v>
       </c>
-      <c r="S69" s="15">
+      <c r="S69" s="14">
         <f>-1872+647+607-332</f>
         <v>-950</v>
       </c>
-      <c r="T69" s="14"/>
+      <c r="T69" s="14">
+        <v>-3192</v>
+      </c>
       <c r="Y69" s="12">
-        <f t="shared" ref="Y69:AH69" si="49">SUM(Y63:Y68)</f>
+        <f t="shared" ref="Y69:AH69" si="59">SUM(Y63:Y68)</f>
         <v>3120</v>
       </c>
       <c r="Z69" s="12">
-        <f t="shared" si="49"/>
+        <f t="shared" si="59"/>
         <v>3555</v>
       </c>
       <c r="AA69" s="12">
-        <f t="shared" si="49"/>
+        <f t="shared" si="59"/>
         <v>3739</v>
       </c>
       <c r="AB69" s="12">
-        <f t="shared" si="49"/>
+        <f t="shared" si="59"/>
         <v>1987</v>
       </c>
       <c r="AC69" s="12">
-        <f t="shared" si="49"/>
+        <f t="shared" si="59"/>
         <v>4908</v>
       </c>
       <c r="AD69" s="12">
-        <f t="shared" si="49"/>
+        <f t="shared" si="59"/>
         <v>8082</v>
       </c>
       <c r="AE69" s="12">
-        <f t="shared" si="49"/>
+        <f t="shared" si="59"/>
         <v>5665</v>
       </c>
       <c r="AF69" s="12">
-        <f t="shared" si="49"/>
+        <f t="shared" si="59"/>
         <v>-1708</v>
       </c>
       <c r="AG69" s="12">
-        <f t="shared" si="49"/>
+        <f t="shared" si="59"/>
         <v>7066</v>
       </c>
       <c r="AH69" s="12">
-        <f t="shared" si="49"/>
+        <f t="shared" si="59"/>
         <v>6837</v>
       </c>
     </row>
@@ -8305,72 +8474,72 @@
         <v>105</v>
       </c>
       <c r="D70" s="12">
-        <f t="shared" ref="D70:P70" si="50">SUM(D64:D69)</f>
+        <f t="shared" ref="D70:P70" si="60">SUM(D64:D69)</f>
         <v>-943</v>
       </c>
       <c r="E70" s="12">
-        <f t="shared" si="50"/>
+        <f t="shared" si="60"/>
         <v>1384</v>
       </c>
       <c r="F70" s="12">
-        <f t="shared" si="50"/>
+        <f t="shared" si="60"/>
         <v>-83</v>
       </c>
       <c r="G70" s="12">
-        <f t="shared" si="50"/>
+        <f t="shared" si="60"/>
         <v>-2066</v>
       </c>
       <c r="H70" s="12">
-        <f t="shared" si="50"/>
+        <f t="shared" si="60"/>
         <v>1127</v>
       </c>
       <c r="I70" s="12">
-        <f t="shared" si="50"/>
+        <f t="shared" si="60"/>
         <v>4995</v>
       </c>
       <c r="J70" s="12">
-        <f t="shared" si="50"/>
+        <f t="shared" si="60"/>
         <v>706</v>
       </c>
       <c r="K70" s="12">
-        <f t="shared" si="50"/>
+        <f t="shared" si="60"/>
         <v>238</v>
       </c>
       <c r="L70" s="12">
-        <f t="shared" si="50"/>
+        <f t="shared" si="60"/>
         <v>-540</v>
       </c>
       <c r="M70" s="12">
-        <f t="shared" si="50"/>
+        <f t="shared" si="60"/>
         <v>4162</v>
       </c>
       <c r="N70" s="12">
-        <f t="shared" si="50"/>
+        <f t="shared" si="60"/>
         <v>3244</v>
       </c>
       <c r="O70" s="12">
-        <f t="shared" si="50"/>
+        <f t="shared" si="60"/>
         <v>-31</v>
       </c>
       <c r="P70" s="12">
-        <f t="shared" si="50"/>
+        <f t="shared" si="60"/>
         <v>138</v>
       </c>
       <c r="Q70" s="12">
         <f>SUM(Q64:Q69)</f>
         <v>2826</v>
       </c>
-      <c r="R70" s="47">
-        <f t="shared" ref="R70:T70" si="51">SUM(R64:R69)</f>
+      <c r="R70" s="12">
+        <f t="shared" ref="R70:T70" si="61">SUM(R64:R69)</f>
         <v>2800</v>
       </c>
-      <c r="S70" s="13">
-        <f t="shared" si="51"/>
+      <c r="S70" s="12">
+        <f t="shared" si="61"/>
         <v>-1561</v>
       </c>
       <c r="T70" s="12">
-        <f t="shared" si="51"/>
-        <v>0</v>
+        <f t="shared" si="61"/>
+        <v>-905</v>
       </c>
       <c r="U70" s="12"/>
       <c r="V70" s="12"/>
@@ -8401,8 +8570,8 @@
       <c r="O71" s="14"/>
       <c r="P71" s="14"/>
       <c r="Q71" s="14"/>
-      <c r="R71" s="48"/>
-      <c r="S71" s="15"/>
+      <c r="R71" s="14"/>
+      <c r="S71" s="14"/>
       <c r="T71" s="14"/>
       <c r="Y71" s="14">
         <v>-1325</v>
@@ -8482,51 +8651,53 @@
       <c r="Q72" s="14">
         <v>-626</v>
       </c>
-      <c r="R72" s="48">
+      <c r="R72" s="14">
         <v>-468</v>
       </c>
-      <c r="S72" s="15">
+      <c r="S72" s="14">
         <v>-558</v>
       </c>
-      <c r="T72" s="14"/>
+      <c r="T72" s="14">
+        <v>-384</v>
+      </c>
       <c r="Y72" s="12">
-        <f t="shared" ref="Y72:AH72" si="52">Y71</f>
+        <f t="shared" ref="Y72:AH72" si="62">Y71</f>
         <v>-1325</v>
       </c>
       <c r="Z72" s="12">
-        <f t="shared" si="52"/>
+        <f t="shared" si="62"/>
         <v>-1830</v>
       </c>
       <c r="AA72" s="12">
-        <f t="shared" si="52"/>
+        <f t="shared" si="62"/>
         <v>-3869</v>
       </c>
       <c r="AB72" s="12">
-        <f t="shared" si="52"/>
+        <f t="shared" si="62"/>
         <v>-2472</v>
       </c>
       <c r="AC72" s="12">
-        <f t="shared" si="52"/>
+        <f t="shared" si="62"/>
         <v>-1939</v>
       </c>
       <c r="AD72" s="12">
-        <f t="shared" si="52"/>
+        <f t="shared" si="62"/>
         <v>-2395</v>
       </c>
       <c r="AE72" s="12">
-        <f t="shared" si="52"/>
+        <f t="shared" si="62"/>
         <v>-6376</v>
       </c>
       <c r="AF72" s="12">
-        <f t="shared" si="52"/>
+        <f t="shared" si="62"/>
         <v>-2301</v>
       </c>
       <c r="AG72" s="12">
-        <f t="shared" si="52"/>
+        <f t="shared" si="62"/>
         <v>-2652</v>
       </c>
       <c r="AH72" s="12">
-        <f t="shared" si="52"/>
+        <f t="shared" si="62"/>
         <v>-2465</v>
       </c>
     </row>
@@ -8535,72 +8706,72 @@
         <v>107</v>
       </c>
       <c r="D73" s="12">
-        <f t="shared" ref="D73:P73" si="53">D72</f>
+        <f t="shared" ref="D73:P73" si="63">D72</f>
         <v>-276</v>
       </c>
       <c r="E73" s="12">
-        <f t="shared" si="53"/>
+        <f t="shared" si="63"/>
         <v>-683</v>
       </c>
       <c r="F73" s="12">
-        <f t="shared" si="53"/>
+        <f t="shared" si="63"/>
         <v>-563</v>
       </c>
       <c r="G73" s="12">
-        <f t="shared" si="53"/>
+        <f t="shared" si="63"/>
         <v>-779</v>
       </c>
       <c r="H73" s="12">
-        <f t="shared" si="53"/>
+        <f t="shared" si="63"/>
         <v>-539</v>
       </c>
       <c r="I73" s="12">
-        <f t="shared" si="53"/>
+        <f t="shared" si="63"/>
         <v>-562</v>
       </c>
       <c r="J73" s="12">
-        <f t="shared" si="53"/>
+        <f t="shared" si="63"/>
         <v>-570</v>
       </c>
       <c r="K73" s="12">
-        <f t="shared" si="53"/>
+        <f t="shared" si="63"/>
         <v>-981</v>
       </c>
       <c r="L73" s="12">
-        <f t="shared" si="53"/>
+        <f t="shared" si="63"/>
         <v>-517</v>
       </c>
       <c r="M73" s="12">
-        <f t="shared" si="53"/>
+        <f t="shared" si="63"/>
         <v>-704</v>
       </c>
       <c r="N73" s="12">
-        <f t="shared" si="53"/>
+        <f t="shared" si="63"/>
         <v>-351</v>
       </c>
       <c r="O73" s="12">
-        <f t="shared" si="53"/>
+        <f t="shared" si="63"/>
         <v>-894</v>
       </c>
       <c r="P73" s="12">
-        <f t="shared" si="53"/>
+        <f t="shared" si="63"/>
         <v>-234</v>
       </c>
       <c r="Q73" s="12">
         <f>Q72</f>
         <v>-626</v>
       </c>
-      <c r="R73" s="47">
-        <f t="shared" ref="R73:T73" si="54">R72</f>
+      <c r="R73" s="12">
+        <f t="shared" ref="R73:T73" si="64">R72</f>
         <v>-468</v>
       </c>
-      <c r="S73" s="13">
-        <f t="shared" si="54"/>
+      <c r="S73" s="12">
+        <f t="shared" si="64"/>
         <v>-558</v>
       </c>
       <c r="T73" s="12">
-        <f t="shared" si="54"/>
-        <v>0</v>
+        <f t="shared" si="64"/>
+        <v>-384</v>
       </c>
       <c r="U73" s="12"/>
       <c r="V73" s="12"/>
@@ -8631,8 +8802,8 @@
       <c r="O74" s="14"/>
       <c r="P74" s="14"/>
       <c r="Q74" s="14"/>
-      <c r="R74" s="48"/>
-      <c r="S74" s="15"/>
+      <c r="R74" s="14"/>
+      <c r="S74" s="14"/>
       <c r="T74" s="14"/>
       <c r="Y74" s="14">
         <v>-945</v>
@@ -8711,13 +8882,15 @@
       <c r="Q75" s="14">
         <v>-286</v>
       </c>
-      <c r="R75" s="48">
+      <c r="R75" s="14">
         <v>0</v>
       </c>
-      <c r="S75" s="15">
+      <c r="S75" s="14">
         <v>-286</v>
       </c>
-      <c r="T75" s="14"/>
+      <c r="T75" s="14">
+        <v>0</v>
+      </c>
       <c r="Y75" s="14">
         <v>-3</v>
       </c>
@@ -8795,13 +8968,15 @@
       <c r="Q76" s="14">
         <v>-1</v>
       </c>
-      <c r="R76" s="48">
+      <c r="R76" s="14">
         <v>0</v>
       </c>
-      <c r="S76" s="15">
+      <c r="S76" s="14">
         <v>0</v>
       </c>
-      <c r="T76" s="14"/>
+      <c r="T76" s="14">
+        <v>0</v>
+      </c>
       <c r="Y76" s="14">
         <f>946-938</f>
         <v>8</v>
@@ -8889,13 +9064,15 @@
       <c r="Q77" s="14">
         <v>-1320</v>
       </c>
-      <c r="R77" s="48">
+      <c r="R77" s="14">
         <v>-1759</v>
       </c>
-      <c r="S77" s="15">
+      <c r="S77" s="14">
         <v>500</v>
       </c>
-      <c r="T77" s="14"/>
+      <c r="T77" s="14">
+        <v>1098</v>
+      </c>
       <c r="Y77" s="14">
         <f>-774-63</f>
         <v>-837</v>
@@ -8983,51 +9160,53 @@
       <c r="Q78" s="14">
         <v>952</v>
       </c>
-      <c r="R78" s="48">
+      <c r="R78" s="14">
         <v>-145</v>
       </c>
-      <c r="S78" s="15">
+      <c r="S78" s="14">
         <v>-272</v>
       </c>
-      <c r="T78" s="14"/>
+      <c r="T78" s="14">
+        <v>133</v>
+      </c>
       <c r="Y78" s="12">
-        <f t="shared" ref="Y78:AH78" si="55">SUM(Y74:Y77)</f>
+        <f t="shared" ref="Y78:AH78" si="65">SUM(Y74:Y77)</f>
         <v>-1777</v>
       </c>
       <c r="Z78" s="12">
-        <f t="shared" si="55"/>
+        <f t="shared" si="65"/>
         <v>-1522</v>
       </c>
       <c r="AA78" s="12">
-        <f t="shared" si="55"/>
+        <f t="shared" si="65"/>
         <v>143</v>
       </c>
       <c r="AB78" s="12">
-        <f t="shared" si="55"/>
+        <f t="shared" si="65"/>
         <v>-88</v>
       </c>
       <c r="AC78" s="12">
-        <f t="shared" si="55"/>
+        <f t="shared" si="65"/>
         <v>-2447</v>
       </c>
       <c r="AD78" s="12">
-        <f t="shared" si="55"/>
+        <f t="shared" si="65"/>
         <v>-1283</v>
       </c>
       <c r="AE78" s="12">
-        <f t="shared" si="55"/>
+        <f t="shared" si="65"/>
         <v>-3358</v>
       </c>
       <c r="AF78" s="12">
-        <f t="shared" si="55"/>
+        <f t="shared" si="65"/>
         <v>3974</v>
       </c>
       <c r="AG78" s="12">
-        <f t="shared" si="55"/>
+        <f t="shared" si="65"/>
         <v>-5160</v>
       </c>
       <c r="AH78" s="12">
-        <f t="shared" si="55"/>
+        <f t="shared" si="65"/>
         <v>-3984</v>
       </c>
     </row>
@@ -9036,15 +9215,15 @@
         <v>112</v>
       </c>
       <c r="D79" s="12">
-        <f t="shared" ref="D79:P79" si="56">SUM(D75:D78)</f>
+        <f t="shared" ref="D79:P79" si="66">SUM(D75:D78)</f>
         <v>1626</v>
       </c>
       <c r="E79" s="12">
-        <f t="shared" si="56"/>
+        <f t="shared" si="66"/>
         <v>-1024</v>
       </c>
       <c r="F79" s="12">
-        <f t="shared" si="56"/>
+        <f t="shared" si="66"/>
         <v>540</v>
       </c>
       <c r="G79" s="12">
@@ -9052,56 +9231,56 @@
         <v>2834</v>
       </c>
       <c r="H79" s="12">
-        <f t="shared" si="56"/>
+        <f t="shared" si="66"/>
         <v>-337</v>
       </c>
       <c r="I79" s="12">
-        <f t="shared" si="56"/>
+        <f t="shared" si="66"/>
         <v>-3081</v>
       </c>
       <c r="J79" s="12">
-        <f t="shared" si="56"/>
+        <f t="shared" si="66"/>
         <v>-1874</v>
       </c>
       <c r="K79" s="12">
-        <f t="shared" si="56"/>
+        <f t="shared" si="66"/>
         <v>130</v>
       </c>
       <c r="L79" s="12">
-        <f t="shared" si="56"/>
+        <f t="shared" si="66"/>
         <v>1364</v>
       </c>
       <c r="M79" s="12">
-        <f t="shared" si="56"/>
+        <f t="shared" si="66"/>
         <v>-3277</v>
       </c>
       <c r="N79" s="12">
-        <f t="shared" si="56"/>
+        <f t="shared" si="66"/>
         <v>-1472</v>
       </c>
       <c r="O79" s="12">
-        <f t="shared" si="56"/>
+        <f t="shared" si="66"/>
         <v>-596</v>
       </c>
       <c r="P79" s="12">
-        <f t="shared" si="56"/>
+        <f t="shared" si="66"/>
         <v>155</v>
       </c>
       <c r="Q79" s="12">
         <f>SUM(Q75:Q78)</f>
         <v>-655</v>
       </c>
-      <c r="R79" s="47">
-        <f t="shared" ref="R79:T79" si="57">SUM(R75:R78)</f>
+      <c r="R79" s="12">
+        <f t="shared" ref="R79:T79" si="67">SUM(R75:R78)</f>
         <v>-1904</v>
       </c>
-      <c r="S79" s="13">
-        <f t="shared" si="57"/>
+      <c r="S79" s="12">
+        <f t="shared" si="67"/>
         <v>-58</v>
       </c>
       <c r="T79" s="12">
-        <f t="shared" si="57"/>
-        <v>0</v>
+        <f t="shared" si="67"/>
+        <v>1231</v>
       </c>
       <c r="U79" s="12"/>
       <c r="V79" s="12"/>
@@ -9133,8 +9312,8 @@
       <c r="O80" s="14"/>
       <c r="P80" s="14"/>
       <c r="Q80" s="14"/>
-      <c r="R80" s="48"/>
-      <c r="S80" s="15"/>
+      <c r="R80" s="14"/>
+      <c r="S80" s="14"/>
       <c r="T80" s="14"/>
       <c r="Y80" s="14">
         <v>25</v>
@@ -9213,13 +9392,15 @@
       <c r="Q81" s="14">
         <v>13</v>
       </c>
-      <c r="R81" s="48">
+      <c r="R81" s="14">
         <v>-8</v>
       </c>
-      <c r="S81" s="15">
+      <c r="S81" s="14">
         <v>-12</v>
       </c>
-      <c r="T81" s="14"/>
+      <c r="T81" s="14">
+        <v>33</v>
+      </c>
       <c r="Y81" s="14"/>
       <c r="Z81" s="14"/>
       <c r="AA81" s="14"/>
@@ -9246,47 +9427,47 @@
       <c r="O82" s="14"/>
       <c r="P82" s="14"/>
       <c r="Q82" s="14"/>
-      <c r="R82" s="48"/>
-      <c r="S82" s="15"/>
+      <c r="R82" s="14"/>
+      <c r="S82" s="14"/>
       <c r="T82" s="14"/>
       <c r="Y82" s="14">
-        <f t="shared" ref="Y82:AH82" si="58">Y69+Y72+Y78+Y80</f>
+        <f t="shared" ref="Y82:AH82" si="68">Y69+Y72+Y78+Y80</f>
         <v>43</v>
       </c>
       <c r="Z82" s="14">
-        <f t="shared" si="58"/>
+        <f t="shared" si="68"/>
         <v>315</v>
       </c>
       <c r="AA82" s="14">
-        <f t="shared" si="58"/>
+        <f t="shared" si="68"/>
         <v>-65</v>
       </c>
       <c r="AB82" s="14">
-        <f t="shared" si="58"/>
+        <f t="shared" si="68"/>
         <v>-526</v>
       </c>
       <c r="AC82" s="14">
-        <f t="shared" si="58"/>
+        <f t="shared" si="68"/>
         <v>565</v>
       </c>
       <c r="AD82" s="14">
-        <f t="shared" si="58"/>
+        <f t="shared" si="68"/>
         <v>4242</v>
       </c>
       <c r="AE82" s="14">
-        <f t="shared" si="58"/>
+        <f t="shared" si="68"/>
         <v>-3943</v>
       </c>
       <c r="AF82" s="14">
-        <f t="shared" si="58"/>
+        <f t="shared" si="68"/>
         <v>119</v>
       </c>
       <c r="AG82" s="14">
-        <f t="shared" si="58"/>
+        <f t="shared" si="68"/>
         <v>-801</v>
       </c>
       <c r="AH82" s="14">
-        <f t="shared" si="58"/>
+        <f t="shared" si="68"/>
         <v>443</v>
       </c>
     </row>
@@ -9295,72 +9476,72 @@
         <v>114</v>
       </c>
       <c r="D83" s="14">
-        <f t="shared" ref="D83:P83" si="59">D70+D73+D79+D81</f>
+        <f t="shared" ref="D83:P83" si="69">D70+D73+D79+D81</f>
         <v>451</v>
       </c>
       <c r="E83" s="14">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>-97</v>
       </c>
       <c r="F83" s="14">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>-137</v>
       </c>
       <c r="G83" s="14">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>-95</v>
       </c>
       <c r="H83" s="14">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>243</v>
       </c>
       <c r="I83" s="14">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>744</v>
       </c>
       <c r="J83" s="14">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>-1796</v>
       </c>
       <c r="K83" s="14">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>-670</v>
       </c>
       <c r="L83" s="14">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>371</v>
       </c>
       <c r="M83" s="14">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>162</v>
       </c>
       <c r="N83" s="14">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>1369</v>
       </c>
       <c r="O83" s="14">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>-1458</v>
       </c>
       <c r="P83" s="14">
-        <f t="shared" si="59"/>
+        <f t="shared" si="69"/>
         <v>-51</v>
       </c>
       <c r="Q83" s="14">
         <f>Q70+Q73+Q79+Q81</f>
         <v>1558</v>
       </c>
-      <c r="R83" s="48">
-        <f t="shared" ref="R83:T83" si="60">R70+R73+R79+R81</f>
+      <c r="R83" s="14">
+        <f t="shared" ref="R83:T83" si="70">R70+R73+R79+R81</f>
         <v>420</v>
       </c>
-      <c r="S83" s="15">
-        <f t="shared" si="60"/>
+      <c r="S83" s="14">
+        <f t="shared" si="70"/>
         <v>-2189</v>
       </c>
       <c r="T83" s="14">
-        <f t="shared" si="60"/>
-        <v>0</v>
+        <f t="shared" si="70"/>
+        <v>-25</v>
       </c>
       <c r="U83" s="14"/>
       <c r="V83" s="14"/>
@@ -9392,51 +9573,51 @@
       <c r="O84" s="14"/>
       <c r="P84" s="14"/>
       <c r="Q84" s="14"/>
-      <c r="R84" s="48"/>
-      <c r="S84" s="15"/>
+      <c r="R84" s="14"/>
+      <c r="S84" s="14"/>
       <c r="T84" s="14"/>
       <c r="U84" s="14"/>
       <c r="V84" s="14"/>
       <c r="W84" s="14"/>
       <c r="X84" s="14"/>
       <c r="Y84" s="14">
-        <f t="shared" ref="Y84:AH84" si="61">Y69+Y71</f>
+        <f t="shared" ref="Y84:AH84" si="71">Y69+Y71</f>
         <v>1795</v>
       </c>
       <c r="Z84" s="14">
-        <f t="shared" si="61"/>
+        <f t="shared" si="71"/>
         <v>1725</v>
       </c>
       <c r="AA84" s="14">
-        <f t="shared" si="61"/>
+        <f t="shared" si="71"/>
         <v>-130</v>
       </c>
       <c r="AB84" s="14">
-        <f t="shared" si="61"/>
+        <f t="shared" si="71"/>
         <v>-485</v>
       </c>
       <c r="AC84" s="14">
-        <f t="shared" si="61"/>
+        <f t="shared" si="71"/>
         <v>2969</v>
       </c>
       <c r="AD84" s="14">
-        <f t="shared" si="61"/>
+        <f t="shared" si="71"/>
         <v>5687</v>
       </c>
       <c r="AE84" s="14">
-        <f t="shared" si="61"/>
+        <f t="shared" si="71"/>
         <v>-711</v>
       </c>
       <c r="AF84" s="14">
-        <f t="shared" si="61"/>
+        <f t="shared" si="71"/>
         <v>-4009</v>
       </c>
       <c r="AG84" s="14">
-        <f t="shared" si="61"/>
+        <f t="shared" si="71"/>
         <v>4414</v>
       </c>
       <c r="AH84" s="14">
-        <f t="shared" si="61"/>
+        <f t="shared" si="71"/>
         <v>4372</v>
       </c>
     </row>
@@ -9445,72 +9626,72 @@
         <v>115</v>
       </c>
       <c r="D85" s="14">
-        <f t="shared" ref="D85:P85" si="62">D70+D72</f>
+        <f t="shared" ref="D85:P85" si="72">D70+D72</f>
         <v>-1219</v>
       </c>
       <c r="E85" s="14">
-        <f t="shared" si="62"/>
+        <f t="shared" si="72"/>
         <v>701</v>
       </c>
       <c r="F85" s="14">
-        <f t="shared" si="62"/>
+        <f t="shared" si="72"/>
         <v>-646</v>
       </c>
       <c r="G85" s="14">
-        <f t="shared" si="62"/>
+        <f t="shared" si="72"/>
         <v>-2845</v>
       </c>
       <c r="H85" s="14">
-        <f t="shared" si="62"/>
+        <f t="shared" si="72"/>
         <v>588</v>
       </c>
       <c r="I85" s="14">
-        <f t="shared" si="62"/>
+        <f t="shared" si="72"/>
         <v>4433</v>
       </c>
       <c r="J85" s="14">
-        <f t="shared" si="62"/>
+        <f t="shared" si="72"/>
         <v>136</v>
       </c>
       <c r="K85" s="14">
-        <f t="shared" si="62"/>
+        <f t="shared" si="72"/>
         <v>-743</v>
       </c>
       <c r="L85" s="14">
-        <f t="shared" si="62"/>
+        <f t="shared" si="72"/>
         <v>-1057</v>
       </c>
       <c r="M85" s="14">
-        <f t="shared" si="62"/>
+        <f t="shared" si="72"/>
         <v>3458</v>
       </c>
       <c r="N85" s="14">
-        <f t="shared" si="62"/>
+        <f t="shared" si="72"/>
         <v>2893</v>
       </c>
       <c r="O85" s="14">
-        <f t="shared" si="62"/>
+        <f t="shared" si="72"/>
         <v>-925</v>
       </c>
       <c r="P85" s="14">
-        <f t="shared" si="62"/>
+        <f t="shared" si="72"/>
         <v>-96</v>
       </c>
       <c r="Q85" s="14">
         <f>Q70+Q72</f>
         <v>2200</v>
       </c>
-      <c r="R85" s="48">
-        <f t="shared" ref="R85:T85" si="63">R70+R72</f>
+      <c r="R85" s="14">
+        <f t="shared" ref="R85:T85" si="73">R70+R72</f>
         <v>2332</v>
       </c>
-      <c r="S85" s="15">
-        <f t="shared" si="63"/>
+      <c r="S85" s="14">
+        <f t="shared" si="73"/>
         <v>-2119</v>
       </c>
       <c r="T85" s="14">
-        <f t="shared" si="63"/>
-        <v>0</v>
+        <f t="shared" si="73"/>
+        <v>-1289</v>
       </c>
       <c r="U85" s="14"/>
       <c r="V85" s="14"/>
@@ -9649,7 +9830,7 @@
       <c r="F5" s="14">
         <v>6793</v>
       </c>
-      <c r="G5" s="54">
+      <c r="G5" s="43">
         <f>SUM(C5:F5)</f>
         <v>32081</v>
       </c>
@@ -9665,7 +9846,7 @@
       <c r="K5" s="14">
         <v>5257</v>
       </c>
-      <c r="L5" s="54">
+      <c r="L5" s="43">
         <f>SUM(H5:K5)</f>
         <v>31758</v>
       </c>
@@ -9681,7 +9862,7 @@
       <c r="P5" s="14">
         <v>5332</v>
       </c>
-      <c r="Q5" s="54">
+      <c r="Q5" s="43">
         <f>SUM(M5:P5)</f>
         <v>28151</v>
       </c>
@@ -9697,17 +9878,19 @@
       <c r="U5" s="14">
         <v>4725</v>
       </c>
-      <c r="V5" s="54">
+      <c r="V5" s="43">
         <f>SUM(R5:U5)</f>
         <v>27788</v>
       </c>
-      <c r="W5" s="14"/>
+      <c r="W5" s="14">
+        <v>8468</v>
+      </c>
       <c r="X5" s="14"/>
       <c r="Y5" s="14"/>
       <c r="Z5" s="14"/>
-      <c r="AA5" s="54">
+      <c r="AA5" s="43">
         <f>SUM(W5:Z5)</f>
-        <v>0</v>
+        <v>8468</v>
       </c>
     </row>
     <row r="6" spans="2:27" x14ac:dyDescent="0.25">
@@ -9781,7 +9964,7 @@
       </c>
       <c r="W6" s="29">
         <f t="shared" ref="W6" si="2">(W5-R5)/R5</f>
-        <v>-1</v>
+        <v>-3.4215328467153285E-2</v>
       </c>
       <c r="X6" s="29">
         <f>(X5-S5)/S5</f>
@@ -9797,7 +9980,7 @@
       </c>
       <c r="AA6" s="34">
         <f t="shared" ref="AA6" si="5">(AA5-V5)/V5</f>
-        <v>-1</v>
+        <v>-0.69526414279545123</v>
       </c>
     </row>
     <row r="7" spans="2:27" x14ac:dyDescent="0.25">
@@ -9856,7 +10039,9 @@
         <v>-0.03</v>
       </c>
       <c r="V7" s="34"/>
-      <c r="W7" s="29"/>
+      <c r="W7" s="29">
+        <v>0.03</v>
+      </c>
       <c r="X7" s="29"/>
       <c r="Y7" s="29"/>
       <c r="Z7" s="29"/>
@@ -9878,7 +10063,7 @@
       <c r="F8" s="14">
         <v>-1252</v>
       </c>
-      <c r="G8" s="54">
+      <c r="G8" s="43">
         <f>SUM(C8:F8)</f>
         <v>1807</v>
       </c>
@@ -9894,7 +10079,7 @@
       <c r="K8" s="14">
         <v>-379</v>
       </c>
-      <c r="L8" s="54">
+      <c r="L8" s="43">
         <f>SUM(H8:K8)</f>
         <v>2705</v>
       </c>
@@ -9910,7 +10095,7 @@
       <c r="P8" s="14">
         <v>-414</v>
       </c>
-      <c r="Q8" s="54">
+      <c r="Q8" s="43">
         <f>SUM(M8:P8)</f>
         <v>2066</v>
       </c>
@@ -9926,17 +10111,19 @@
       <c r="U8" s="14">
         <v>-327</v>
       </c>
-      <c r="V8" s="54">
+      <c r="V8" s="43">
         <f>SUM(R8:U8)</f>
         <v>2147</v>
       </c>
-      <c r="W8" s="14"/>
+      <c r="W8" s="14">
+        <v>1308</v>
+      </c>
       <c r="X8" s="14"/>
       <c r="Y8" s="14"/>
       <c r="Z8" s="14"/>
-      <c r="AA8" s="54">
+      <c r="AA8" s="43">
         <f>SUM(W8:Z8)</f>
-        <v>0</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="9" spans="2:27" x14ac:dyDescent="0.25">
@@ -10023,9 +10210,9 @@
         <f t="shared" si="6"/>
         <v>7.7263567007341299E-2</v>
       </c>
-      <c r="W9" s="31" t="e">
+      <c r="W9" s="31">
         <f t="shared" ref="W9:AA9" si="7">W8/W5</f>
-        <v>#DIV/0!</v>
+        <v>0.15446386395843173</v>
       </c>
       <c r="X9" s="31" t="e">
         <f t="shared" si="7"/>
@@ -10039,9 +10226,9 @@
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AA9" s="35" t="e">
+      <c r="AA9" s="35">
         <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
+        <v>0.15446386395843173</v>
       </c>
     </row>
     <row r="10" spans="2:27" x14ac:dyDescent="0.25">
@@ -10070,7 +10257,7 @@
       <c r="F11" s="14">
         <v>1470</v>
       </c>
-      <c r="G11" s="54">
+      <c r="G11" s="43">
         <f>SUM(C11:F11)</f>
         <v>13605</v>
       </c>
@@ -10086,7 +10273,7 @@
       <c r="K11" s="14">
         <v>1326</v>
       </c>
-      <c r="L11" s="54">
+      <c r="L11" s="43">
         <f>SUM(H11:K11)</f>
         <v>12965</v>
       </c>
@@ -10102,7 +10289,7 @@
       <c r="P11" s="14">
         <v>1264</v>
       </c>
-      <c r="Q11" s="54">
+      <c r="Q11" s="43">
         <f>SUM(M11:P11)</f>
         <v>12281</v>
       </c>
@@ -10118,17 +10305,19 @@
       <c r="U11" s="14">
         <v>981</v>
       </c>
-      <c r="V11" s="54">
+      <c r="V11" s="43">
         <f>SUM(R11:U11)</f>
         <v>11493</v>
       </c>
-      <c r="W11" s="14"/>
+      <c r="W11" s="14">
+        <v>3743</v>
+      </c>
       <c r="X11" s="14"/>
       <c r="Y11" s="14"/>
       <c r="Z11" s="14"/>
-      <c r="AA11" s="54">
+      <c r="AA11" s="43">
         <f>SUM(W11:Z11)</f>
-        <v>0</v>
+        <v>3743</v>
       </c>
     </row>
     <row r="12" spans="2:27" x14ac:dyDescent="0.25">
@@ -10202,7 +10391,7 @@
       </c>
       <c r="W12" s="29">
         <f t="shared" ref="W12" si="19">(W11-R11)/R11</f>
-        <v>-1</v>
+        <v>-7.4660074165636595E-2</v>
       </c>
       <c r="X12" s="29">
         <f>(X11-S11)/S11</f>
@@ -10218,7 +10407,7 @@
       </c>
       <c r="AA12" s="34">
         <f t="shared" ref="AA12" si="22">(AA11-V11)/V11</f>
-        <v>-1</v>
+        <v>-0.67432350126163754</v>
       </c>
     </row>
     <row r="13" spans="2:27" x14ac:dyDescent="0.25">
@@ -10277,7 +10466,9 @@
         <v>-0.1</v>
       </c>
       <c r="V13" s="34"/>
-      <c r="W13" s="29"/>
+      <c r="W13" s="29">
+        <v>-0.01</v>
+      </c>
       <c r="X13" s="29"/>
       <c r="Y13" s="29"/>
       <c r="Z13" s="29"/>
@@ -10299,7 +10490,7 @@
       <c r="F14" s="14">
         <v>-468</v>
       </c>
-      <c r="G14" s="54">
+      <c r="G14" s="43">
         <f>SUM(C14:F14)</f>
         <v>918</v>
       </c>
@@ -10315,7 +10506,7 @@
       <c r="K14" s="14">
         <v>-407</v>
       </c>
-      <c r="L14" s="54">
+      <c r="L14" s="43">
         <f>SUM(H14:K14)</f>
         <v>950</v>
       </c>
@@ -10331,7 +10522,7 @@
       <c r="P14" s="14">
         <v>-467</v>
       </c>
-      <c r="Q14" s="54">
+      <c r="Q14" s="43">
         <f>SUM(M14:P14)</f>
         <v>741</v>
       </c>
@@ -10347,17 +10538,19 @@
       <c r="U14" s="14">
         <v>-377</v>
       </c>
-      <c r="V14" s="54">
+      <c r="V14" s="43">
         <f>SUM(R14:U14)</f>
         <v>729</v>
       </c>
-      <c r="W14" s="14"/>
+      <c r="W14" s="14">
+        <v>447</v>
+      </c>
       <c r="X14" s="14"/>
       <c r="Y14" s="14"/>
       <c r="Z14" s="14"/>
-      <c r="AA14" s="54">
+      <c r="AA14" s="43">
         <f>SUM(W14:Z14)</f>
-        <v>0</v>
+        <v>447</v>
       </c>
     </row>
     <row r="15" spans="2:27" x14ac:dyDescent="0.25">
@@ -10444,9 +10637,9 @@
         <f t="shared" si="23"/>
         <v>6.3429913860610809E-2</v>
       </c>
-      <c r="W15" s="31" t="e">
+      <c r="W15" s="31">
         <f t="shared" ref="W15:AA15" si="24">W14/W11</f>
-        <v>#DIV/0!</v>
+        <v>0.11942292278920652</v>
       </c>
       <c r="X15" s="31" t="e">
         <f t="shared" si="24"/>
@@ -10460,9 +10653,9 @@
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AA15" s="35" t="e">
+      <c r="AA15" s="35">
         <f t="shared" si="24"/>
-        <v>#DIV/0!</v>
+        <v>0.11942292278920652</v>
       </c>
     </row>
     <row r="16" spans="2:27" x14ac:dyDescent="0.25">
@@ -10491,7 +10684,7 @@
       <c r="F17" s="14">
         <v>2071</v>
       </c>
-      <c r="G17" s="54">
+      <c r="G17" s="43">
         <f>SUM(C17:F17)</f>
         <v>8233</v>
       </c>
@@ -10507,7 +10700,7 @@
       <c r="K17" s="14">
         <v>1968</v>
       </c>
-      <c r="L17" s="54">
+      <c r="L17" s="43">
         <f>SUM(H17:K17)</f>
         <v>8398</v>
       </c>
@@ -10523,7 +10716,7 @@
       <c r="P17" s="14">
         <v>1820</v>
       </c>
-      <c r="Q17" s="54">
+      <c r="Q17" s="43">
         <f>SUM(M17:P17)</f>
         <v>7765</v>
       </c>
@@ -10539,17 +10732,19 @@
       <c r="U17" s="14">
         <v>1676</v>
       </c>
-      <c r="V17" s="54">
+      <c r="V17" s="43">
         <f>SUM(R17:U17)</f>
         <v>7177</v>
       </c>
-      <c r="W17" s="14"/>
+      <c r="W17" s="14">
+        <v>1712</v>
+      </c>
       <c r="X17" s="14"/>
       <c r="Y17" s="14"/>
       <c r="Z17" s="14"/>
-      <c r="AA17" s="54">
+      <c r="AA17" s="43">
         <f>SUM(W17:Z17)</f>
-        <v>0</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="18" spans="2:27" x14ac:dyDescent="0.25">
@@ -10623,7 +10818,7 @@
       </c>
       <c r="W18" s="29">
         <f t="shared" ref="W18" si="36">(W17-R17)/R17</f>
-        <v>-1</v>
+        <v>-7.8082929456112005E-2</v>
       </c>
       <c r="X18" s="29">
         <f>(X17-S17)/S17</f>
@@ -10639,7 +10834,7 @@
       </c>
       <c r="AA18" s="34">
         <f t="shared" ref="AA18" si="39">(AA17-V17)/V17</f>
-        <v>-1</v>
+        <v>-0.76146022014769399</v>
       </c>
     </row>
     <row r="19" spans="2:27" x14ac:dyDescent="0.25">
@@ -10698,7 +10893,9 @@
         <v>0.02</v>
       </c>
       <c r="V19" s="34"/>
-      <c r="W19" s="29"/>
+      <c r="W19" s="29">
+        <v>0.01</v>
+      </c>
       <c r="X19" s="29"/>
       <c r="Y19" s="29"/>
       <c r="Z19" s="29"/>
@@ -10720,7 +10917,7 @@
       <c r="F20" s="14">
         <v>80</v>
       </c>
-      <c r="G20" s="54">
+      <c r="G20" s="43">
         <f>SUM(C20:F20)</f>
         <v>714</v>
       </c>
@@ -10736,7 +10933,7 @@
       <c r="K20" s="14">
         <v>-4</v>
       </c>
-      <c r="L20" s="54">
+      <c r="L20" s="43">
         <f>SUM(H20:K20)</f>
         <v>755</v>
       </c>
@@ -10752,7 +10949,7 @@
       <c r="P20" s="14">
         <v>-239</v>
       </c>
-      <c r="Q20" s="54">
+      <c r="Q20" s="43">
         <f>SUM(M20:P20)</f>
         <v>318</v>
       </c>
@@ -10768,17 +10965,19 @@
       <c r="U20" s="14">
         <v>63</v>
       </c>
-      <c r="V20" s="54">
+      <c r="V20" s="43">
         <f>SUM(R20:U20)</f>
         <v>640</v>
       </c>
-      <c r="W20" s="14"/>
+      <c r="W20" s="14">
+        <v>110</v>
+      </c>
       <c r="X20" s="14"/>
       <c r="Y20" s="14"/>
       <c r="Z20" s="14"/>
-      <c r="AA20" s="54">
+      <c r="AA20" s="43">
         <f>SUM(W20:Z20)</f>
-        <v>0</v>
+        <v>110</v>
       </c>
     </row>
     <row r="21" spans="2:27" x14ac:dyDescent="0.25">
@@ -10865,9 +11064,9 @@
         <f t="shared" si="40"/>
         <v>8.9173749477497566E-2</v>
       </c>
-      <c r="W21" s="31" t="e">
+      <c r="W21" s="31">
         <f t="shared" ref="W21:AA21" si="41">W20/W17</f>
-        <v>#DIV/0!</v>
+        <v>6.4252336448598124E-2</v>
       </c>
       <c r="X21" s="31" t="e">
         <f t="shared" si="41"/>
@@ -10881,9 +11080,9 @@
         <f t="shared" si="41"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AA21" s="35" t="e">
+      <c r="AA21" s="35">
         <f t="shared" si="41"/>
-        <v>#DIV/0!</v>
+        <v>6.4252336448598124E-2</v>
       </c>
     </row>
   </sheetData>
@@ -10893,7 +11092,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE82810A-3E55-C349-A3D0-E0F5837F2D04}">
-  <dimension ref="A6:I51"/>
+  <dimension ref="A6:I68"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="10.83203125" style="2"/>
@@ -10902,232 +11101,232 @@
   </cols>
   <sheetData>
     <row r="6" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C6" s="55" t="s">
+      <c r="C6" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="D6" s="55"/>
-      <c r="E6" s="55" t="s">
+      <c r="D6" s="44"/>
+      <c r="E6" s="44" t="s">
         <v>141</v>
       </c>
-      <c r="F6" s="55"/>
-      <c r="G6" s="55" t="s">
+      <c r="F6" s="44"/>
+      <c r="G6" s="44" t="s">
         <v>29</v>
       </c>
-      <c r="H6" s="55" t="s">
+      <c r="H6" s="44" t="s">
         <v>142</v>
       </c>
-      <c r="I6" s="55" t="s">
+      <c r="I6" s="44" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="7" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C7" s="56" t="s">
+      <c r="C7" s="45" t="s">
         <v>123</v>
       </c>
-      <c r="D7" s="56"/>
-      <c r="E7" s="57">
+      <c r="D7" s="45"/>
+      <c r="E7" s="46">
         <v>2200</v>
       </c>
-      <c r="F7" s="57"/>
-      <c r="G7" s="57">
-        <v>7</v>
-      </c>
-      <c r="H7" s="57">
+      <c r="F7" s="46"/>
+      <c r="G7" s="46">
+        <v>10</v>
+      </c>
+      <c r="H7" s="46">
         <f>E7*G7</f>
-        <v>15400</v>
-      </c>
-      <c r="I7" s="58">
+        <v>22000</v>
+      </c>
+      <c r="I7" s="47">
         <f>H7/Modell!$B$5</f>
-        <v>26.937204827706836</v>
+        <v>38.481721182438342</v>
       </c>
     </row>
     <row r="8" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C8" s="56" t="s">
+      <c r="C8" s="45" t="s">
         <v>127</v>
       </c>
-      <c r="D8" s="56"/>
-      <c r="E8" s="57">
+      <c r="D8" s="45"/>
+      <c r="E8" s="46">
         <v>750</v>
       </c>
-      <c r="F8" s="57"/>
-      <c r="G8" s="57">
+      <c r="F8" s="46"/>
+      <c r="G8" s="46">
         <v>8</v>
       </c>
-      <c r="H8" s="57">
+      <c r="H8" s="46">
         <f t="shared" ref="H8:H9" si="0">E8*G8</f>
         <v>6000</v>
       </c>
-      <c r="I8" s="58">
+      <c r="I8" s="47">
         <f>H8/Modell!$B$5</f>
         <v>10.495014867937728</v>
       </c>
     </row>
     <row r="9" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C9" s="56" t="s">
+      <c r="C9" s="45" t="s">
         <v>128</v>
       </c>
-      <c r="D9" s="56"/>
-      <c r="E9" s="57">
+      <c r="D9" s="45"/>
+      <c r="E9" s="46">
         <v>700</v>
       </c>
-      <c r="F9" s="57"/>
-      <c r="G9" s="57">
+      <c r="F9" s="46"/>
+      <c r="G9" s="46">
         <v>6</v>
       </c>
-      <c r="H9" s="57">
+      <c r="H9" s="46">
         <f t="shared" si="0"/>
         <v>4200</v>
       </c>
-      <c r="I9" s="58">
+      <c r="I9" s="47">
         <f>H9/Modell!$B$5</f>
         <v>7.3465104075564103</v>
       </c>
     </row>
     <row r="10" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C10" s="55" t="s">
+      <c r="C10" s="44" t="s">
         <v>144</v>
       </c>
-      <c r="D10" s="55"/>
-      <c r="E10" s="59"/>
-      <c r="F10" s="59"/>
-      <c r="G10" s="59"/>
-      <c r="H10" s="59">
+      <c r="D10" s="44"/>
+      <c r="E10" s="48"/>
+      <c r="F10" s="48"/>
+      <c r="G10" s="48"/>
+      <c r="H10" s="48">
         <f>SUM(H7:H9)</f>
-        <v>25600</v>
-      </c>
-      <c r="I10" s="60">
+        <v>32200</v>
+      </c>
+      <c r="I10" s="49">
         <f>SUM(I7:I9)</f>
-        <v>44.778730103200971</v>
+        <v>56.323246457932477</v>
       </c>
     </row>
     <row r="11" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C11" s="61"/>
-      <c r="D11" s="61"/>
-      <c r="E11" s="61"/>
-      <c r="F11" s="61"/>
-      <c r="G11" s="61"/>
-      <c r="H11" s="61"/>
-      <c r="I11" s="61"/>
+      <c r="C11" s="50"/>
+      <c r="D11" s="50"/>
+      <c r="E11" s="50"/>
+      <c r="F11" s="50"/>
+      <c r="G11" s="50"/>
+      <c r="H11" s="50"/>
+      <c r="I11" s="50"/>
     </row>
     <row r="12" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C12" s="56" t="s">
+      <c r="C12" s="45" t="s">
         <v>82</v>
       </c>
-      <c r="D12" s="56"/>
-      <c r="E12" s="56"/>
-      <c r="F12" s="56"/>
-      <c r="G12" s="56"/>
-      <c r="H12" s="57">
+      <c r="D12" s="45"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="45"/>
+      <c r="G12" s="45"/>
+      <c r="H12" s="46">
         <f>Modell!B7</f>
-        <v>1707</v>
-      </c>
-      <c r="I12" s="58">
+        <v>1708</v>
+      </c>
+      <c r="I12" s="47">
         <f>H12/Modell!$B$5</f>
-        <v>2.9858317299282837</v>
+        <v>2.98758089907294</v>
       </c>
     </row>
     <row r="13" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C13" s="56" t="s">
+      <c r="C13" s="45" t="s">
         <v>145</v>
       </c>
-      <c r="D13" s="56"/>
-      <c r="E13" s="56"/>
-      <c r="F13" s="56"/>
-      <c r="G13" s="56"/>
-      <c r="H13" s="57">
+      <c r="D13" s="45"/>
+      <c r="E13" s="45"/>
+      <c r="F13" s="45"/>
+      <c r="G13" s="45"/>
+      <c r="H13" s="46">
         <f>-Modell!B8</f>
-        <v>-9816</v>
-      </c>
-      <c r="I13" s="58">
+        <v>-9106</v>
+      </c>
+      <c r="I13" s="47">
         <f>H13/Modell!$B$5</f>
-        <v>-17.169844323946123</v>
+        <v>-15.92793423124016</v>
       </c>
     </row>
     <row r="14" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C14" s="55" t="s">
+      <c r="C14" s="44" t="s">
         <v>146</v>
       </c>
-      <c r="D14" s="55"/>
-      <c r="E14" s="55"/>
-      <c r="F14" s="55"/>
-      <c r="G14" s="55"/>
-      <c r="H14" s="59">
+      <c r="D14" s="44"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="44"/>
+      <c r="G14" s="44"/>
+      <c r="H14" s="48">
         <f>SUM(H10:H13)</f>
-        <v>17491</v>
-      </c>
-      <c r="I14" s="60">
+        <v>24802</v>
+      </c>
+      <c r="I14" s="49">
         <f>SUM(I10:I13)</f>
-        <v>30.594717509183134</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="45" t="s">
+        <v>43.382893125765257</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="B44" s="62">
-        <f>I7</f>
-        <v>26.937204827706836</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="45" t="s">
+      <c r="B61" s="51">
+        <f t="shared" ref="B61:B68" si="1">I7</f>
+        <v>38.481721182438342</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="B45" s="62">
-        <f t="shared" ref="B45:B51" si="1">I8</f>
+      <c r="B62" s="51">
+        <f t="shared" si="1"/>
         <v>10.495014867937728</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="45" t="s">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B46" s="62">
+      <c r="B63" s="51">
         <f t="shared" si="1"/>
         <v>7.3465104075564103</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="53" t="s">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B47" s="62">
+      <c r="B64" s="51">
         <f t="shared" si="1"/>
-        <v>44.778730103200971</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="63"/>
-      <c r="B48" s="62">
+        <v>56.323246457932477</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" s="52"/>
+      <c r="B65" s="51">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="45" t="s">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B49" s="62">
+      <c r="B66" s="51">
         <f t="shared" si="1"/>
-        <v>2.9858317299282837</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="45" t="s">
+        <v>2.98758089907294</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="B50" s="62">
+      <c r="B67" s="51">
         <f t="shared" si="1"/>
-        <v>-17.169844323946123</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="53" t="s">
+        <v>-15.92793423124016</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B51" s="62">
+      <c r="B68" s="51">
         <f t="shared" si="1"/>
-        <v>30.594717509183134</v>
+        <v>43.382893125765257</v>
       </c>
     </row>
   </sheetData>
@@ -11138,7 +11337,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEC8E745-DC06-8448-81B5-DC40131426CF}">
-  <dimension ref="C4:G6"/>
+  <dimension ref="C4:F6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="29.5" bestFit="1" customWidth="1"/>
@@ -11147,61 +11346,50 @@
     <col min="7" max="7" width="18.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="3:7" ht="62" x14ac:dyDescent="0.7">
+    <row r="4" spans="3:6" ht="62" x14ac:dyDescent="0.7">
       <c r="C4" s="23"/>
       <c r="D4" s="23">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E4" s="23">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="F4" s="23">
-        <v>2027</v>
-      </c>
-      <c r="G4" s="64">
         <v>2028</v>
       </c>
     </row>
-    <row r="5" spans="3:7" ht="62" x14ac:dyDescent="0.7">
+    <row r="5" spans="3:6" ht="62" x14ac:dyDescent="0.7">
       <c r="C5" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="38">
-        <f>Modell!$B$9/Modell!AI10</f>
-        <v>11.050239737840636</v>
-      </c>
-      <c r="E5" s="38">
+      <c r="D5" s="36">
         <f>Modell!$B$9/Modell!AJ10</f>
-        <v>10.58408718463795</v>
-      </c>
-      <c r="F5" s="38">
+        <v>12.002536860907551</v>
+      </c>
+      <c r="E5" s="36">
         <f>Modell!$B$9/Modell!AK10</f>
-        <v>10.275812800619367</v>
-      </c>
-      <c r="G5" s="38">
+        <v>11.652948408648133</v>
+      </c>
+      <c r="F5" s="36">
         <f>Modell!$B$9/Modell!AL10</f>
-        <v>9.8805892313647838</v>
-      </c>
-    </row>
-    <row r="6" spans="3:7" ht="62" x14ac:dyDescent="0.7">
+        <v>11.204758085238582</v>
+      </c>
+    </row>
+    <row r="6" spans="3:6" ht="62" x14ac:dyDescent="0.7">
       <c r="C6" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="38">
-        <f>Modell!$B$4/Modell!AI16</f>
-        <v>13.517313559322035</v>
-      </c>
-      <c r="E6" s="38">
+      <c r="D6" s="36">
         <f>Modell!$B$4/Modell!AJ16</f>
-        <v>9.8811424564208927</v>
-      </c>
-      <c r="F6" s="38">
+        <v>11.692938080118536</v>
+      </c>
+      <c r="E6" s="36">
         <f>Modell!$B$4/Modell!AK16</f>
-        <v>9.593342190699893</v>
-      </c>
-      <c r="G6" s="38">
+        <v>11.352367068076273</v>
+      </c>
+      <c r="F6" s="36">
         <f>Modell!$B$4/Modell!AL16</f>
-        <v>9.2243674910575972</v>
+        <v>10.915737565457947</v>
       </c>
     </row>
   </sheetData>
@@ -11373,7 +11561,7 @@
       </c>
     </row>
     <row r="5" spans="1:179" x14ac:dyDescent="0.25">
-      <c r="A5" s="39">
+      <c r="A5" s="37">
         <f>AA21</f>
         <v>38.720238849988995</v>
       </c>
@@ -11457,7 +11645,7 @@
     <row r="6" spans="1:179" x14ac:dyDescent="0.25">
       <c r="A6" s="18">
         <f>AA22</f>
-        <v>-7.4785212664540177E-2</v>
+        <v>-0.15291536097158184</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>57</v>
@@ -11507,7 +11695,7 @@
         <v>14100</v>
       </c>
       <c r="O6" s="14">
-        <f t="shared" ref="N6:X6" si="4">SUM(O4:O5)</f>
+        <f t="shared" ref="O6:X6" si="4">SUM(O4:O5)</f>
         <v>12119.64</v>
       </c>
       <c r="P6" s="14">
@@ -11837,7 +12025,7 @@
         <v>2899</v>
       </c>
       <c r="O10" s="12">
-        <f t="shared" ref="N10:X10" si="10">SUM(O6:O9)</f>
+        <f t="shared" ref="O10:X10" si="10">SUM(O6:O9)</f>
         <v>2343.9199999999996</v>
       </c>
       <c r="P10" s="12">
@@ -12004,7 +12192,7 @@
         <v>2149</v>
       </c>
       <c r="O12" s="14">
-        <f t="shared" ref="N12:X12" si="13">SUM(O10:O11)</f>
+        <f t="shared" ref="O12:X12" si="13">SUM(O10:O11)</f>
         <v>2343.9199999999996</v>
       </c>
       <c r="P12" s="14">
@@ -12171,7 +12359,7 @@
         <v>1770</v>
       </c>
       <c r="O14" s="12">
-        <f t="shared" ref="N14:X14" si="17">SUM(O12:O13)</f>
+        <f t="shared" ref="O14:X14" si="17">SUM(O12:O13)</f>
         <v>1875.1359999999997</v>
       </c>
       <c r="P14" s="12">
@@ -12948,7 +13136,7 @@
         <v>3.0960293860416299</v>
       </c>
       <c r="O16" s="19">
-        <f t="shared" ref="N16:X16" si="22">O14/O15</f>
+        <f t="shared" ref="O16:X16" si="22">O14/O15</f>
         <v>3.2799300332342129</v>
       </c>
       <c r="P16" s="19">
@@ -13052,7 +13240,7 @@
         <v>-3.5944738583719389E-2</v>
       </c>
       <c r="O18" s="18">
-        <f t="shared" ref="N18:X18" si="25">(O4-N4)/N4</f>
+        <f t="shared" ref="O18:X18" si="25">(O4-N4)/N4</f>
         <v>0</v>
       </c>
       <c r="P18" s="18">
@@ -13300,14 +13488,14 @@
       </c>
     </row>
     <row r="22" spans="1:27" s="26" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="40"/>
-      <c r="N22" s="40"/>
-      <c r="Z22" s="41" t="s">
+      <c r="B22" s="38"/>
+      <c r="N22" s="38"/>
+      <c r="Z22" s="39" t="s">
         <v>122</v>
       </c>
-      <c r="AA22" s="42">
+      <c r="AA22" s="40">
         <f>(AA21-Modell!B4)/Modell!B4</f>
-        <v>-7.4785212664540177E-2</v>
+        <v>-0.15291536097158184</v>
       </c>
     </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.25">
@@ -13316,7 +13504,7 @@
       </c>
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A24" s="39">
+      <c r="A24" s="37">
         <f>AA42</f>
         <v>33.59856686803306</v>
       </c>
@@ -13387,7 +13575,7 @@
     <row r="25" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A25" s="18">
         <f>AA43</f>
-        <v>-0.19716686097889941</v>
+        <v>-0.26496243999052593</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>55</v>
@@ -15138,7 +15326,7 @@
         <v>-3.5944738583719389E-2</v>
       </c>
       <c r="O39" s="18">
-        <f t="shared" ref="N39:X39" si="114">(O25-N25)/N25</f>
+        <f t="shared" ref="O39:X39" si="114">(O25-N25)/N25</f>
         <v>-1.9999999999999976E-2</v>
       </c>
       <c r="P39" s="18">
@@ -15386,14 +15574,14 @@
       </c>
     </row>
     <row r="43" spans="2:179" s="26" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="40"/>
-      <c r="N43" s="40"/>
-      <c r="Z43" s="41" t="s">
+      <c r="B43" s="38"/>
+      <c r="N43" s="38"/>
+      <c r="Z43" s="39" t="s">
         <v>122</v>
       </c>
-      <c r="AA43" s="42">
+      <c r="AA43" s="40">
         <f>(AA42-Modell!B4)/Modell!B4</f>
-        <v>-0.19716686097889941</v>
+        <v>-0.26496243999052593</v>
       </c>
     </row>
   </sheetData>
